--- a/jogos_2026-04-06.xlsx
+++ b/jogos_2026-04-06.xlsx
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>4.6</v>
+        <v>2.45</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.68</v>
+        <v>3.06</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>6.18</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>6.18</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.99</v>
+        <v>3.15</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.22</v>
+        <v>3.36</v>
       </c>
       <c r="R47" t="n">
-        <v>3.94</v>
+        <v>2.21</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.38</v>
+        <v>3.25</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.65</v>
+        <v>3.42</v>
       </c>
       <c r="R48" t="n">
-        <v>7.85</v>
+        <v>2.14</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3.25</v>
+        <v>1.99</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.42</v>
+        <v>3.22</v>
       </c>
       <c r="R49" t="n">
-        <v>2.14</v>
+        <v>3.94</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.77</v>
+        <v>1.98</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12081,10 +12081,10 @@
         <v>0</v>
       </c>
       <c r="AG59" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH59" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17991,10 +17991,10 @@
         <v>0</v>
       </c>
       <c r="AG89" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH89" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.08</v>
+        <v>1.49</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.74</v>
+        <v>4.7</v>
       </c>
       <c r="R95" t="n">
-        <v>3.13</v>
+        <v>5.45</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>7.75</v>
+        <v>1.83</v>
       </c>
       <c r="Q105" t="n">
-        <v>5.99</v>
+        <v>4</v>
       </c>
       <c r="R105" t="n">
-        <v>1.33</v>
+        <v>3.98</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1.83</v>
+        <v>4.25</v>
       </c>
       <c r="Q107" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="R107" t="n">
-        <v>3.98</v>
+        <v>1.8</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>1.87</v>
+        <v>7.75</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.99</v>
+        <v>5.99</v>
       </c>
       <c r="R108" t="n">
-        <v>3.81</v>
+        <v>1.33</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24289,10 +24289,10 @@
         <v>0</v>
       </c>
       <c r="AE121" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF121" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25077,10 +25077,10 @@
         <v>0</v>
       </c>
       <c r="AE125" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF125" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG125" t="n">
         <v>0</v>
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="Q130" t="n">
-        <v>4.97</v>
+        <v>3.48</v>
       </c>
       <c r="R130" t="n">
-        <v>9.9</v>
+        <v>2.14</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26062,10 +26062,10 @@
         <v>0</v>
       </c>
       <c r="AE130" t="n">
-        <v>1.93</v>
+        <v>1.66</v>
       </c>
       <c r="AF130" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AG130" t="n">
         <v>0</v>
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="Q132" t="n">
-        <v>3.48</v>
+        <v>3.71</v>
       </c>
       <c r="R132" t="n">
-        <v>2.06</v>
+        <v>3.61</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.71</v>
+        <v>3.48</v>
       </c>
       <c r="R133" t="n">
-        <v>3.61</v>
+        <v>2.06</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,22 +27151,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,22 +27545,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27638,10 +27638,10 @@
         <v>0</v>
       </c>
       <c r="AE138" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF138" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG138" t="n">
         <v>0</v>
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1.77</v>
+        <v>2.6</v>
       </c>
       <c r="Q139" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="R139" t="n">
-        <v>4.61</v>
+        <v>2.62</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27835,10 +27835,10 @@
         <v>0</v>
       </c>
       <c r="AE139" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="AF139" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AG139" t="n">
         <v>0</v>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28032,10 +28032,10 @@
         <v>0</v>
       </c>
       <c r="AE140" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AF140" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG140" t="n">
         <v>0</v>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28377,137 +28377,137 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P142" t="n">
         <v>2.5</v>
       </c>
       <c r="Q142" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R142" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S142" t="n">
         <v>3.1</v>
       </c>
-      <c r="R142" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="S142" t="n">
-        <v>0</v>
-      </c>
       <c r="T142" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U142" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V142" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W142" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="X142" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y142" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z142" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA142" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB142" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC142" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD142" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AE142" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF142" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG142" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AH142" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI142" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="AJ142" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK142" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL142" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM142" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN142" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO142" t="n">
         <v>0</v>
       </c>
       <c r="AP142" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ142" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR142" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS142" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AT142" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AU142" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="AV142" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AW142" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AX142" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY142" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ142" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BA142" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BB142" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC142" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD142" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE142" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF142" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG142" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28574,137 +28574,137 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P143" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="Q143" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="R143" t="n">
-        <v>2.48</v>
+        <v>3.55</v>
       </c>
       <c r="S143" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T143" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U143" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="V143" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W143" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="X143" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Y143" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z143" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB143" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC143" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD143" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AE143" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF143" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AG143" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AH143" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI143" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="AJ143" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK143" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL143" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM143" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN143" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AO143" t="n">
         <v>0</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ143" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AR143" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AS143" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AT143" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AU143" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="AV143" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AW143" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AX143" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AY143" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ143" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BA143" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="BB143" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC143" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BD143" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE143" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BF143" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG143" t="n">
         <v>0</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="Q144" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="R144" t="n">
-        <v>3.55</v>
+        <v>2.8</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31288,22 +31288,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q157" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R157" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31381,10 +31381,10 @@
         <v>0</v>
       </c>
       <c r="AE157" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF157" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG157" t="n">
         <v>0</v>
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,22 +31879,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q162" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R162" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32366,10 +32366,10 @@
         <v>0</v>
       </c>
       <c r="AE162" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF162" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG162" t="n">
         <v>0</v>

--- a/jogos_2026-04-06.xlsx
+++ b/jogos_2026-04-06.xlsx
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>6.18</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>6.18</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3.25</v>
+        <v>4.08</v>
       </c>
       <c r="Q48" t="n">
         <v>3.42</v>
       </c>
       <c r="R48" t="n">
-        <v>2.14</v>
+        <v>1.89</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.99</v>
+        <v>3.15</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.22</v>
+        <v>3.36</v>
       </c>
       <c r="R49" t="n">
-        <v>3.94</v>
+        <v>2.21</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.38</v>
+        <v>1.99</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.65</v>
+        <v>3.22</v>
       </c>
       <c r="R50" t="n">
-        <v>7.85</v>
+        <v>3.94</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.98</v>
+        <v>1.72</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12081,10 +12081,10 @@
         <v>0</v>
       </c>
       <c r="AG59" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15627,10 +15627,10 @@
         <v>0</v>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH77" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.08</v>
+        <v>2.33</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.74</v>
+        <v>3.1</v>
       </c>
       <c r="R94" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>7.75</v>
+        <v>4.25</v>
       </c>
       <c r="Q108" t="n">
-        <v>5.99</v>
+        <v>3.89</v>
       </c>
       <c r="R108" t="n">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24289,10 +24289,10 @@
         <v>0</v>
       </c>
       <c r="AE121" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF121" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG121" t="n">
         <v>0</v>
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24486,10 +24486,10 @@
         <v>0</v>
       </c>
       <c r="AE122" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF122" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG122" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,22 +25575,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q128" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25668,10 +25668,10 @@
         <v>0</v>
       </c>
       <c r="AE128" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF128" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG128" t="n">
         <v>0</v>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,22 +25969,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26062,10 +26062,10 @@
         <v>0</v>
       </c>
       <c r="AE130" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF130" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG130" t="n">
         <v>0</v>
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="Q132" t="n">
-        <v>3.71</v>
+        <v>3.48</v>
       </c>
       <c r="R132" t="n">
-        <v>3.61</v>
+        <v>2.06</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.48</v>
+        <v>3.71</v>
       </c>
       <c r="R133" t="n">
-        <v>2.06</v>
+        <v>3.61</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27638,10 +27638,10 @@
         <v>0</v>
       </c>
       <c r="AE138" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF138" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG138" t="n">
         <v>0</v>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28032,10 +28032,10 @@
         <v>0</v>
       </c>
       <c r="AE140" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF140" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG140" t="n">
         <v>0</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q144" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R144" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q145" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R145" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>1.94</v>
+        <v>2.62</v>
       </c>
       <c r="Q152" t="n">
-        <v>3.64</v>
+        <v>3.13</v>
       </c>
       <c r="R152" t="n">
-        <v>3.63</v>
+        <v>3.19</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30396,10 +30396,10 @@
         <v>0</v>
       </c>
       <c r="AE152" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AF152" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AG152" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>2.62</v>
+        <v>1.94</v>
       </c>
       <c r="Q153" t="n">
-        <v>3.13</v>
+        <v>3.64</v>
       </c>
       <c r="R153" t="n">
-        <v>3.19</v>
+        <v>3.63</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30593,10 +30593,10 @@
         <v>0</v>
       </c>
       <c r="AE153" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AF153" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AG153" t="n">
         <v>0</v>
@@ -31288,22 +31288,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,22 +31879,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q161" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R161" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32169,10 +32169,10 @@
         <v>0</v>
       </c>
       <c r="AE161" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF161" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG161" t="n">
         <v>0</v>
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q162" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R162" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32366,10 +32366,10 @@
         <v>0</v>
       </c>
       <c r="AE162" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF162" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG162" t="n">
         <v>0</v>

--- a/jogos_2026-04-06.xlsx
+++ b/jogos_2026-04-06.xlsx
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.38</v>
+        <v>1.99</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.65</v>
+        <v>3.22</v>
       </c>
       <c r="R46" t="n">
-        <v>7.85</v>
+        <v>3.94</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.98</v>
+        <v>1.72</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3.15</v>
+        <v>4.08</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="R49" t="n">
-        <v>2.21</v>
+        <v>1.89</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15627,10 +15627,10 @@
         <v>0</v>
       </c>
       <c r="AG77" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>3.01</v>
+        <v>1.6</v>
       </c>
       <c r="Q78" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="R78" t="n">
-        <v>2.52</v>
+        <v>4.81</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15824,10 +15824,10 @@
         <v>0</v>
       </c>
       <c r="AG78" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH78" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.08</v>
+        <v>2.33</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.74</v>
+        <v>3.1</v>
       </c>
       <c r="R93" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.33</v>
+        <v>2.08</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.1</v>
+        <v>3.74</v>
       </c>
       <c r="R94" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q118" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q134" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q150" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R150" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>

--- a/jogos_2026-04-06.xlsx
+++ b/jogos_2026-04-06.xlsx
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.38</v>
+        <v>3.25</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.65</v>
+        <v>3.42</v>
       </c>
       <c r="R47" t="n">
-        <v>7.85</v>
+        <v>2.14</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>4.08</v>
+        <v>3.15</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.42</v>
+        <v>3.36</v>
       </c>
       <c r="R49" t="n">
-        <v>1.89</v>
+        <v>2.21</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15824,10 +15824,10 @@
         <v>0</v>
       </c>
       <c r="AG78" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH78" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16218,10 +16218,10 @@
         <v>0</v>
       </c>
       <c r="AG80" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH80" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1.83</v>
+        <v>4.25</v>
       </c>
       <c r="Q110" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="R110" t="n">
-        <v>3.98</v>
+        <v>1.8</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.99</v>
+        <v>4</v>
       </c>
       <c r="R111" t="n">
-        <v>3.81</v>
+        <v>3.98</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24486,10 +24486,10 @@
         <v>0</v>
       </c>
       <c r="AE122" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF122" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG122" t="n">
         <v>0</v>
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24880,10 +24880,10 @@
         <v>0</v>
       </c>
       <c r="AE124" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF124" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG124" t="n">
         <v>0</v>
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="Q132" t="n">
-        <v>3.48</v>
+        <v>3.71</v>
       </c>
       <c r="R132" t="n">
-        <v>2.06</v>
+        <v>3.61</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.71</v>
+        <v>3.48</v>
       </c>
       <c r="R133" t="n">
-        <v>3.61</v>
+        <v>2.06</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -27151,22 +27151,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27441,10 +27441,10 @@
         <v>0</v>
       </c>
       <c r="AE137" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF137" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q139" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27835,10 +27835,10 @@
         <v>0</v>
       </c>
       <c r="AE139" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AF139" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG139" t="n">
         <v>0</v>
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1.77</v>
+        <v>2.6</v>
       </c>
       <c r="Q140" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="R140" t="n">
-        <v>4.61</v>
+        <v>2.62</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28032,10 +28032,10 @@
         <v>0</v>
       </c>
       <c r="AE140" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="AF140" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AG140" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q143" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q144" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R144" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="Q145" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="R145" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G162" t="n">

--- a/jogos_2026-04-06.xlsx
+++ b/jogos_2026-04-06.xlsx
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>6.18</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>6.18</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>3.25</v>
+        <v>1.38</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.42</v>
+        <v>4.65</v>
       </c>
       <c r="R47" t="n">
-        <v>2.14</v>
+        <v>7.85</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.38</v>
+        <v>4.08</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.65</v>
+        <v>3.42</v>
       </c>
       <c r="R48" t="n">
-        <v>7.85</v>
+        <v>1.89</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3.15</v>
+        <v>1.99</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.36</v>
+        <v>3.22</v>
       </c>
       <c r="R49" t="n">
-        <v>2.21</v>
+        <v>3.94</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>4.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="R50" t="n">
-        <v>1.89</v>
+        <v>3.31</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.99</v>
+        <v>2.24</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.22</v>
+        <v>3.02</v>
       </c>
       <c r="R54" t="n">
-        <v>3.94</v>
+        <v>3.38</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.98</v>
+        <v>1.76</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.72</v>
+        <v>1.93</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14248,10 +14248,10 @@
         <v>0</v>
       </c>
       <c r="AG70" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH70" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16218,10 +16218,10 @@
         <v>0</v>
       </c>
       <c r="AG80" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.33</v>
+        <v>1.49</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="R93" t="n">
-        <v>3.12</v>
+        <v>5.45</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.49</v>
+        <v>2.08</v>
       </c>
       <c r="Q95" t="n">
-        <v>4.7</v>
+        <v>3.74</v>
       </c>
       <c r="R95" t="n">
-        <v>5.45</v>
+        <v>3.13</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>7.75</v>
+        <v>2.53</v>
       </c>
       <c r="Q109" t="n">
-        <v>5.99</v>
+        <v>3.32</v>
       </c>
       <c r="R109" t="n">
-        <v>1.33</v>
+        <v>2.63</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF109" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1.83</v>
+        <v>2.91</v>
       </c>
       <c r="Q111" t="n">
-        <v>4</v>
+        <v>2.97</v>
       </c>
       <c r="R111" t="n">
-        <v>3.98</v>
+        <v>2.56</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1.87</v>
+        <v>4.25</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.99</v>
+        <v>3.89</v>
       </c>
       <c r="R112" t="n">
-        <v>3.81</v>
+        <v>1.8</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24880,10 +24880,10 @@
         <v>0</v>
       </c>
       <c r="AE124" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF124" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG124" t="n">
         <v>0</v>
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25077,10 +25077,10 @@
         <v>0</v>
       </c>
       <c r="AE125" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF125" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG125" t="n">
         <v>0</v>
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25471,10 +25471,10 @@
         <v>0</v>
       </c>
       <c r="AE127" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF127" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG127" t="n">
         <v>0</v>
@@ -25575,22 +25575,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25668,10 +25668,10 @@
         <v>0</v>
       </c>
       <c r="AE128" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF128" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG128" t="n">
         <v>0</v>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.48</v>
+        <v>3.56</v>
       </c>
       <c r="R133" t="n">
-        <v>2.06</v>
+        <v>2.35</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="Q134" t="n">
-        <v>3.56</v>
+        <v>3.48</v>
       </c>
       <c r="R134" t="n">
-        <v>2.35</v>
+        <v>2.06</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -27151,22 +27151,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27638,10 +27638,10 @@
         <v>0</v>
       </c>
       <c r="AE138" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF138" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG138" t="n">
         <v>0</v>
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28032,10 +28032,10 @@
         <v>0</v>
       </c>
       <c r="AE140" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AF140" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG140" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q143" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R143" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q144" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R144" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="Q145" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="R145" t="n">
-        <v>3.55</v>
+        <v>2.8</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q157" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R157" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31381,10 +31381,10 @@
         <v>0</v>
       </c>
       <c r="AE157" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF157" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG157" t="n">
         <v>0</v>
@@ -31682,22 +31682,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -32076,22 +32076,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q161" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R161" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32169,10 +32169,10 @@
         <v>0</v>
       </c>
       <c r="AE161" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF161" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG161" t="n">
         <v>0</v>

--- a/jogos_2026-04-06.xlsx
+++ b/jogos_2026-04-06.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.45</v>
+        <v>4.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.06</v>
+        <v>3.68</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="R21" t="n">
-        <v>2.36</v>
+        <v>2.41</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.77</v>
+        <v>2.07</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.24</v>
+        <v>3.68</v>
       </c>
       <c r="R30" t="n">
-        <v>2.33</v>
+        <v>3.14</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.07</v>
+        <v>1.92</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="R31" t="n">
-        <v>3.14</v>
+        <v>3.58</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.92</v>
+        <v>2.53</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.8</v>
+        <v>3.14</v>
       </c>
       <c r="R35" t="n">
-        <v>3.58</v>
+        <v>2.74</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3.25</v>
+        <v>1.38</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.42</v>
+        <v>4.65</v>
       </c>
       <c r="R45" t="n">
-        <v>2.14</v>
+        <v>7.85</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.38</v>
+        <v>3.15</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.65</v>
+        <v>3.36</v>
       </c>
       <c r="R47" t="n">
-        <v>7.85</v>
+        <v>2.21</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>4.08</v>
+        <v>1.99</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.42</v>
+        <v>3.22</v>
       </c>
       <c r="R48" t="n">
-        <v>1.89</v>
+        <v>3.94</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.24</v>
+        <v>1.75</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.02</v>
+        <v>3.84</v>
       </c>
       <c r="R54" t="n">
-        <v>3.38</v>
+        <v>4.18</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.75</v>
+        <v>3.25</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.84</v>
+        <v>3.42</v>
       </c>
       <c r="R55" t="n">
-        <v>4.18</v>
+        <v>2.14</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11884,10 +11884,10 @@
         <v>0</v>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14248,10 +14248,10 @@
         <v>0</v>
       </c>
       <c r="AG70" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH70" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.08</v>
+        <v>1.49</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.74</v>
+        <v>4.7</v>
       </c>
       <c r="R95" t="n">
-        <v>3.13</v>
+        <v>5.45</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.99</v>
+        <v>4</v>
       </c>
       <c r="R107" t="n">
-        <v>3.81</v>
+        <v>3.98</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.53</v>
+        <v>4.25</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.32</v>
+        <v>3.89</v>
       </c>
       <c r="R109" t="n">
-        <v>2.63</v>
+        <v>1.8</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF109" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF110" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24683,10 +24683,10 @@
         <v>0</v>
       </c>
       <c r="AE123" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF123" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG123" t="n">
         <v>0</v>
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25077,10 +25077,10 @@
         <v>0</v>
       </c>
       <c r="AE125" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF125" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG125" t="n">
         <v>0</v>
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25471,10 +25471,10 @@
         <v>0</v>
       </c>
       <c r="AE127" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF127" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG127" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,22 +25772,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q129" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25865,10 +25865,10 @@
         <v>0</v>
       </c>
       <c r="AE129" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF129" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG129" t="n">
         <v>0</v>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>2</v>
+        <v>3.24</v>
       </c>
       <c r="Q132" t="n">
-        <v>3.71</v>
+        <v>3.56</v>
       </c>
       <c r="R132" t="n">
-        <v>3.61</v>
+        <v>2.35</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>3.24</v>
+        <v>2</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.56</v>
+        <v>3.71</v>
       </c>
       <c r="R133" t="n">
-        <v>2.35</v>
+        <v>3.61</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27441,10 +27441,10 @@
         <v>0</v>
       </c>
       <c r="AE137" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF137" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG137" t="n">
         <v>0</v>
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>2.6</v>
+        <v>1.77</v>
       </c>
       <c r="Q138" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="R138" t="n">
-        <v>2.62</v>
+        <v>4.61</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27638,10 +27638,10 @@
         <v>0</v>
       </c>
       <c r="AE138" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="AF138" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AG138" t="n">
         <v>0</v>
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q139" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R139" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27835,10 +27835,10 @@
         <v>0</v>
       </c>
       <c r="AE139" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF139" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG139" t="n">
         <v>0</v>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28377,137 +28377,137 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P142" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q142" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S142" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T142" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U142" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="V142" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W142" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="X142" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Y142" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z142" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB142" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC142" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD142" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AE142" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF142" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AG142" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AH142" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI142" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="AJ142" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK142" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL142" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM142" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN142" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AO142" t="n">
         <v>0</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ142" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AR142" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AS142" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AT142" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AU142" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="AV142" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AW142" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AX142" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AY142" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ142" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BA142" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="BB142" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC142" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BD142" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE142" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BF142" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG142" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28574,137 +28574,137 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P143" t="n">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="Q143" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="R143" t="n">
-        <v>3.55</v>
+        <v>2.48</v>
       </c>
       <c r="S143" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T143" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U143" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V143" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W143" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="X143" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y143" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z143" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA143" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB143" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC143" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD143" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AE143" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF143" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG143" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AH143" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI143" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="AJ143" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK143" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL143" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM143" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN143" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO143" t="n">
         <v>0</v>
       </c>
       <c r="AP143" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR143" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS143" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AT143" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AU143" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="AV143" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AW143" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AX143" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY143" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ143" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BA143" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BB143" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC143" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD143" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE143" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF143" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG143" t="n">
         <v>0</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q144" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R144" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="Q145" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="R145" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31288,22 +31288,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q157" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R157" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31381,10 +31381,10 @@
         <v>0</v>
       </c>
       <c r="AE157" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF157" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG157" t="n">
         <v>0</v>
@@ -31485,22 +31485,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q158" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R158" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31578,10 +31578,10 @@
         <v>0</v>
       </c>
       <c r="AE158" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF158" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG158" t="n">
         <v>0</v>
@@ -31682,22 +31682,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,22 +31879,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32076,22 +32076,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,22 +32273,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G162" t="n">

--- a/jogos_2026-04-06.xlsx
+++ b/jogos_2026-04-06.xlsx
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.45</v>
+        <v>4.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.06</v>
+        <v>3.68</v>
       </c>
       <c r="R8" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>4.6</v>
+        <v>2.45</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.68</v>
+        <v>3.06</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>6.18</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>6.18</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.07</v>
+        <v>3.37</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.68</v>
+        <v>4.24</v>
       </c>
       <c r="R30" t="n">
-        <v>3.14</v>
+        <v>1.94</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.92</v>
+        <v>2.53</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.8</v>
+        <v>3.14</v>
       </c>
       <c r="R31" t="n">
-        <v>3.58</v>
+        <v>2.74</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.53</v>
+        <v>1.59</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.14</v>
+        <v>4.1</v>
       </c>
       <c r="R35" t="n">
-        <v>2.74</v>
+        <v>4.99</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.19</v>
+        <v>1.92</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="R39" t="n">
-        <v>2.85</v>
+        <v>3.58</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>7.85</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>3.15</v>
+        <v>2.24</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.36</v>
+        <v>3.02</v>
       </c>
       <c r="R47" t="n">
-        <v>2.21</v>
+        <v>3.38</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.99</v>
+        <v>1.38</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.22</v>
+        <v>4.65</v>
       </c>
       <c r="R48" t="n">
-        <v>3.94</v>
+        <v>7.85</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF48" t="n">
         <v>1.98</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>1.72</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>4.08</v>
+        <v>3.25</v>
       </c>
       <c r="Q51" t="n">
         <v>3.42</v>
       </c>
       <c r="R51" t="n">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.24</v>
+        <v>4.08</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.02</v>
+        <v>3.42</v>
       </c>
       <c r="R52" t="n">
-        <v>3.38</v>
+        <v>1.89</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.84</v>
+        <v>3.22</v>
       </c>
       <c r="R54" t="n">
-        <v>4.18</v>
+        <v>3.94</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="R55" t="n">
-        <v>2.14</v>
+        <v>3.31</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11884,10 +11884,10 @@
         <v>0</v>
       </c>
       <c r="AG58" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>3.01</v>
+        <v>1.6</v>
       </c>
       <c r="Q65" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="R65" t="n">
-        <v>2.52</v>
+        <v>4.81</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13263,10 +13263,10 @@
         <v>0</v>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.33</v>
+        <v>1.49</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="R94" t="n">
-        <v>3.12</v>
+        <v>5.45</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.49</v>
+        <v>2.08</v>
       </c>
       <c r="Q95" t="n">
-        <v>4.7</v>
+        <v>3.74</v>
       </c>
       <c r="R95" t="n">
-        <v>5.45</v>
+        <v>3.13</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1.87</v>
+        <v>4.25</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.99</v>
+        <v>3.89</v>
       </c>
       <c r="R105" t="n">
-        <v>3.81</v>
+        <v>1.8</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1.83</v>
+        <v>2.53</v>
       </c>
       <c r="Q107" t="n">
-        <v>4</v>
+        <v>3.32</v>
       </c>
       <c r="R107" t="n">
-        <v>3.98</v>
+        <v>2.63</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21531,10 +21531,10 @@
         <v>0</v>
       </c>
       <c r="AE107" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF107" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG107" t="n">
         <v>0</v>
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2.53</v>
+        <v>2.91</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.32</v>
+        <v>2.97</v>
       </c>
       <c r="R110" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF110" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25274,10 +25274,10 @@
         <v>0</v>
       </c>
       <c r="AE126" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF126" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG126" t="n">
         <v>0</v>
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,22 +25772,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25865,10 +25865,10 @@
         <v>0</v>
       </c>
       <c r="AE129" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF129" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG129" t="n">
         <v>0</v>
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>3.24</v>
+        <v>2</v>
       </c>
       <c r="Q132" t="n">
-        <v>3.56</v>
+        <v>3.71</v>
       </c>
       <c r="R132" t="n">
-        <v>2.35</v>
+        <v>3.61</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>2</v>
+        <v>3.24</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.71</v>
+        <v>3.56</v>
       </c>
       <c r="R133" t="n">
-        <v>3.61</v>
+        <v>2.35</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -27151,22 +27151,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q136" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R136" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27244,10 +27244,10 @@
         <v>0</v>
       </c>
       <c r="AE136" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF136" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG136" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27638,10 +27638,10 @@
         <v>0</v>
       </c>
       <c r="AE138" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF138" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG138" t="n">
         <v>0</v>
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q139" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27835,10 +27835,10 @@
         <v>0</v>
       </c>
       <c r="AE139" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AF139" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG139" t="n">
         <v>0</v>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28032,10 +28032,10 @@
         <v>0</v>
       </c>
       <c r="AE140" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF140" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG140" t="n">
         <v>0</v>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q142" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R142" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28574,137 +28574,137 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P143" t="n">
         <v>2.5</v>
       </c>
       <c r="Q143" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R143" t="n">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="S143" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T143" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U143" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="V143" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W143" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="X143" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Y143" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z143" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB143" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC143" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD143" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AE143" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF143" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AG143" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AH143" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI143" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="AJ143" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK143" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL143" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM143" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN143" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AO143" t="n">
         <v>0</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ143" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AR143" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AS143" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AT143" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AU143" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="AV143" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AW143" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AX143" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AY143" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ143" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BA143" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="BB143" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC143" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BD143" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE143" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BF143" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG143" t="n">
         <v>0</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28771,137 +28771,137 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P144" t="n">
         <v>2.5</v>
       </c>
       <c r="Q144" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R144" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S144" t="n">
         <v>3.1</v>
       </c>
-      <c r="R144" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="S144" t="n">
-        <v>0</v>
-      </c>
       <c r="T144" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U144" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V144" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W144" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="X144" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y144" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z144" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA144" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB144" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC144" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD144" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AE144" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF144" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG144" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AH144" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI144" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="AJ144" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK144" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL144" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM144" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN144" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO144" t="n">
         <v>0</v>
       </c>
       <c r="AP144" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ144" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR144" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS144" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AT144" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AU144" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="AV144" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AW144" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AX144" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY144" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ144" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BA144" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BB144" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC144" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD144" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE144" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF144" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG144" t="n">
         <v>0</v>
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R145" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>2.62</v>
+        <v>1.94</v>
       </c>
       <c r="Q152" t="n">
-        <v>3.13</v>
+        <v>3.64</v>
       </c>
       <c r="R152" t="n">
-        <v>3.19</v>
+        <v>3.63</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30396,10 +30396,10 @@
         <v>0</v>
       </c>
       <c r="AE152" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AF152" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AG152" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>1.94</v>
+        <v>2.62</v>
       </c>
       <c r="Q153" t="n">
-        <v>3.64</v>
+        <v>3.13</v>
       </c>
       <c r="R153" t="n">
-        <v>3.63</v>
+        <v>3.19</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30593,10 +30593,10 @@
         <v>0</v>
       </c>
       <c r="AE153" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AF153" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AG153" t="n">
         <v>0</v>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31485,22 +31485,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q158" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R158" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31578,10 +31578,10 @@
         <v>0</v>
       </c>
       <c r="AE158" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF158" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG158" t="n">
         <v>0</v>
@@ -31682,22 +31682,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31927,13 +31927,13 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q160" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R160" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
@@ -31972,10 +31972,10 @@
         <v>0</v>
       </c>
       <c r="AE160" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF160" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG160" t="n">
         <v>0</v>
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G162" t="n">

--- a/jogos_2026-04-06.xlsx
+++ b/jogos_2026-04-06.xlsx
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>4.6</v>
+        <v>2.45</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.68</v>
+        <v>3.06</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.45</v>
+        <v>4.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.06</v>
+        <v>3.68</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>6.18</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>6.18</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.53</v>
+        <v>1.59</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.14</v>
+        <v>4.1</v>
       </c>
       <c r="R31" t="n">
-        <v>2.74</v>
+        <v>4.99</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.77</v>
+        <v>2.19</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.24</v>
+        <v>3.75</v>
       </c>
       <c r="R36" t="n">
-        <v>2.33</v>
+        <v>2.85</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.9</v>
+        <v>2.53</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.6</v>
+        <v>3.14</v>
       </c>
       <c r="R37" t="n">
-        <v>3.4</v>
+        <v>2.74</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.92</v>
+        <v>2.77</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.8</v>
+        <v>3.24</v>
       </c>
       <c r="R39" t="n">
-        <v>3.58</v>
+        <v>2.33</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3.15</v>
+        <v>1.99</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.36</v>
+        <v>3.22</v>
       </c>
       <c r="R46" t="n">
-        <v>2.21</v>
+        <v>3.94</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.24</v>
+        <v>1.75</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.02</v>
+        <v>3.84</v>
       </c>
       <c r="R47" t="n">
-        <v>3.38</v>
+        <v>4.18</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.38</v>
+        <v>4.08</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.65</v>
+        <v>3.42</v>
       </c>
       <c r="R48" t="n">
-        <v>7.85</v>
+        <v>1.89</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.42</v>
+        <v>3.36</v>
       </c>
       <c r="R51" t="n">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>4.08</v>
+        <v>3.25</v>
       </c>
       <c r="Q52" t="n">
         <v>3.42</v>
       </c>
       <c r="R52" t="n">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13263,10 +13263,10 @@
         <v>0</v>
       </c>
       <c r="AG65" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17400,10 +17400,10 @@
         <v>0</v>
       </c>
       <c r="AG86" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH86" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.33</v>
+        <v>2.08</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.1</v>
+        <v>3.74</v>
       </c>
       <c r="R93" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.08</v>
+        <v>1.49</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.74</v>
+        <v>4.7</v>
       </c>
       <c r="R95" t="n">
-        <v>3.13</v>
+        <v>5.45</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>4.25</v>
+        <v>1.83</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.89</v>
+        <v>4</v>
       </c>
       <c r="R105" t="n">
-        <v>1.8</v>
+        <v>3.98</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21334,10 +21334,10 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF106" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21531,10 +21531,10 @@
         <v>0</v>
       </c>
       <c r="AE107" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF107" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG107" t="n">
         <v>0</v>
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2.91</v>
+        <v>4.25</v>
       </c>
       <c r="Q110" t="n">
-        <v>2.97</v>
+        <v>3.89</v>
       </c>
       <c r="R110" t="n">
-        <v>2.56</v>
+        <v>1.8</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1.83</v>
+        <v>7.75</v>
       </c>
       <c r="Q111" t="n">
-        <v>4</v>
+        <v>5.99</v>
       </c>
       <c r="R111" t="n">
-        <v>3.98</v>
+        <v>1.33</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1.87</v>
+        <v>2.91</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.99</v>
+        <v>2.97</v>
       </c>
       <c r="R112" t="n">
-        <v>3.81</v>
+        <v>2.56</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24683,10 +24683,10 @@
         <v>0</v>
       </c>
       <c r="AE123" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF123" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG123" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25274,10 +25274,10 @@
         <v>0</v>
       </c>
       <c r="AE126" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF126" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG126" t="n">
         <v>0</v>
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25471,10 +25471,10 @@
         <v>0</v>
       </c>
       <c r="AE127" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF127" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG127" t="n">
         <v>0</v>
@@ -25575,22 +25575,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q128" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25668,10 +25668,10 @@
         <v>0</v>
       </c>
       <c r="AE128" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF128" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG128" t="n">
         <v>0</v>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="Q132" t="n">
-        <v>3.71</v>
+        <v>3.48</v>
       </c>
       <c r="R132" t="n">
-        <v>3.61</v>
+        <v>2.06</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>3.24</v>
+        <v>2</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.56</v>
+        <v>3.71</v>
       </c>
       <c r="R133" t="n">
-        <v>2.35</v>
+        <v>3.61</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="Q134" t="n">
-        <v>3.48</v>
+        <v>3.56</v>
       </c>
       <c r="R134" t="n">
-        <v>2.06</v>
+        <v>2.35</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q139" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R139" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27835,10 +27835,10 @@
         <v>0</v>
       </c>
       <c r="AE139" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF139" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG139" t="n">
         <v>0</v>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28032,10 +28032,10 @@
         <v>0</v>
       </c>
       <c r="AE140" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AF140" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG140" t="n">
         <v>0</v>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28377,137 +28377,137 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P142" t="n">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="Q142" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="R142" t="n">
-        <v>3.55</v>
+        <v>2.48</v>
       </c>
       <c r="S142" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T142" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U142" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V142" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W142" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="X142" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y142" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z142" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA142" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB142" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC142" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD142" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AE142" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF142" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG142" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AH142" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI142" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="AJ142" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK142" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL142" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM142" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN142" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO142" t="n">
         <v>0</v>
       </c>
       <c r="AP142" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ142" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR142" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS142" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AT142" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AU142" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="AV142" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AW142" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AX142" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY142" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ142" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BA142" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BB142" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC142" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD142" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE142" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF142" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG142" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q143" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28771,137 +28771,137 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P144" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="Q144" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="R144" t="n">
-        <v>2.48</v>
+        <v>3.55</v>
       </c>
       <c r="S144" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T144" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U144" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="V144" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W144" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="X144" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Y144" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z144" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB144" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC144" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD144" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AE144" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF144" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AG144" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AH144" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI144" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="AJ144" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK144" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL144" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM144" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN144" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AO144" t="n">
         <v>0</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AR144" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AS144" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AT144" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AU144" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="AV144" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AW144" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AX144" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AY144" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ144" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BA144" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="BB144" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC144" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BD144" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE144" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BF144" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG144" t="n">
         <v>0</v>
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q145" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R145" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31288,22 +31288,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31485,22 +31485,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,22 +31682,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -32076,22 +32076,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G162" t="n">

--- a/jogos_2026-04-06.xlsx
+++ b/jogos_2026-04-06.xlsx
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.45</v>
+        <v>4.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.06</v>
+        <v>3.68</v>
       </c>
       <c r="R8" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.59</v>
+        <v>1.92</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="R31" t="n">
-        <v>4.99</v>
+        <v>3.58</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.19</v>
+        <v>2.77</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.75</v>
+        <v>3.24</v>
       </c>
       <c r="R36" t="n">
-        <v>2.85</v>
+        <v>2.33</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.77</v>
+        <v>2.53</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.24</v>
+        <v>3.14</v>
       </c>
       <c r="R39" t="n">
-        <v>2.33</v>
+        <v>2.74</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.37</v>
+        <v>1.59</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.24</v>
+        <v>4.1</v>
       </c>
       <c r="R41" t="n">
-        <v>1.94</v>
+        <v>4.99</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="R42" t="n">
-        <v>3.58</v>
+        <v>3.14</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.38</v>
+        <v>3.84</v>
       </c>
       <c r="R45" t="n">
-        <v>3.31</v>
+        <v>4.18</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.84</v>
+        <v>3.38</v>
       </c>
       <c r="R47" t="n">
-        <v>4.18</v>
+        <v>3.31</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>4.08</v>
+        <v>3.25</v>
       </c>
       <c r="Q48" t="n">
         <v>3.42</v>
       </c>
       <c r="R48" t="n">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.42</v>
+        <v>3.36</v>
       </c>
       <c r="R52" t="n">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16218,10 +16218,10 @@
         <v>0</v>
       </c>
       <c r="AG80" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH80" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17400,10 +17400,10 @@
         <v>0</v>
       </c>
       <c r="AG86" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH86" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.08</v>
+        <v>1.49</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.74</v>
+        <v>4.7</v>
       </c>
       <c r="R93" t="n">
-        <v>3.13</v>
+        <v>5.45</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.49</v>
+        <v>2.08</v>
       </c>
       <c r="Q95" t="n">
-        <v>4.7</v>
+        <v>3.74</v>
       </c>
       <c r="R95" t="n">
-        <v>5.45</v>
+        <v>3.13</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1.83</v>
+        <v>2.53</v>
       </c>
       <c r="Q105" t="n">
-        <v>4</v>
+        <v>3.32</v>
       </c>
       <c r="R105" t="n">
-        <v>3.98</v>
+        <v>2.63</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21137,10 +21137,10 @@
         <v>0</v>
       </c>
       <c r="AE105" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF105" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG105" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>2.53</v>
+        <v>2.91</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.32</v>
+        <v>2.97</v>
       </c>
       <c r="R106" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21334,10 +21334,10 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF106" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>7.75</v>
+        <v>1.87</v>
       </c>
       <c r="Q111" t="n">
-        <v>5.99</v>
+        <v>3.99</v>
       </c>
       <c r="R111" t="n">
-        <v>1.33</v>
+        <v>3.81</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24486,10 +24486,10 @@
         <v>0</v>
       </c>
       <c r="AE122" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF122" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG122" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25471,10 +25471,10 @@
         <v>0</v>
       </c>
       <c r="AE127" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF127" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG127" t="n">
         <v>0</v>
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q136" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27244,10 +27244,10 @@
         <v>0</v>
       </c>
       <c r="AE136" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF136" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG136" t="n">
         <v>0</v>
@@ -27545,22 +27545,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>2.6</v>
+        <v>1.77</v>
       </c>
       <c r="Q139" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="R139" t="n">
-        <v>2.62</v>
+        <v>4.61</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27835,10 +27835,10 @@
         <v>0</v>
       </c>
       <c r="AE139" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="AF139" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AG139" t="n">
         <v>0</v>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28032,10 +28032,10 @@
         <v>0</v>
       </c>
       <c r="AE140" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF140" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG140" t="n">
         <v>0</v>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28377,137 +28377,137 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P142" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="Q142" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="R142" t="n">
-        <v>2.48</v>
+        <v>3.55</v>
       </c>
       <c r="S142" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T142" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U142" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="V142" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W142" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="X142" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Y142" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z142" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB142" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC142" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD142" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AE142" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF142" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AG142" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AH142" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI142" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="AJ142" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK142" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL142" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM142" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN142" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AO142" t="n">
         <v>0</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ142" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AR142" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AS142" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AT142" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AU142" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="AV142" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AW142" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AX142" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AY142" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ142" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BA142" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="BB142" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC142" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BD142" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE142" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BF142" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG142" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28574,137 +28574,137 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P143" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q143" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R143" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S143" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T143" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U143" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V143" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W143" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="X143" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y143" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z143" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA143" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB143" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC143" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD143" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AE143" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF143" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG143" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AH143" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI143" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="AJ143" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK143" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL143" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM143" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN143" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO143" t="n">
         <v>0</v>
       </c>
       <c r="AP143" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR143" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS143" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AT143" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AU143" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="AV143" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AW143" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AX143" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY143" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ143" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BA143" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BB143" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC143" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD143" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE143" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF143" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG143" t="n">
         <v>0</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q144" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R144" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q157" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R157" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31381,10 +31381,10 @@
         <v>0</v>
       </c>
       <c r="AE157" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF157" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG157" t="n">
         <v>0</v>
@@ -31485,22 +31485,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31927,13 +31927,13 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q160" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R160" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
@@ -31972,10 +31972,10 @@
         <v>0</v>
       </c>
       <c r="AE160" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF160" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG160" t="n">
         <v>0</v>
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,22 +32273,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G162" t="n">

--- a/jogos_2026-04-06.xlsx
+++ b/jogos_2026-04-06.xlsx
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.19</v>
+        <v>3.37</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.75</v>
+        <v>4.24</v>
       </c>
       <c r="R34" t="n">
-        <v>2.85</v>
+        <v>1.94</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.77</v>
+        <v>1.92</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.24</v>
+        <v>3.8</v>
       </c>
       <c r="R36" t="n">
-        <v>2.33</v>
+        <v>3.58</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.53</v>
+        <v>2.07</v>
       </c>
       <c r="Q39" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="R39" t="n">
         <v>3.14</v>
-      </c>
-      <c r="R39" t="n">
-        <v>2.74</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.59</v>
+        <v>2.53</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.1</v>
+        <v>3.14</v>
       </c>
       <c r="R41" t="n">
-        <v>4.99</v>
+        <v>2.74</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.07</v>
+        <v>2.77</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.68</v>
+        <v>3.24</v>
       </c>
       <c r="R42" t="n">
-        <v>3.14</v>
+        <v>2.33</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.1</v>
+        <v>1.38</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.38</v>
+        <v>4.65</v>
       </c>
       <c r="R47" t="n">
-        <v>3.31</v>
+        <v>7.85</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3.25</v>
+        <v>2.24</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.42</v>
+        <v>3.02</v>
       </c>
       <c r="R48" t="n">
-        <v>2.14</v>
+        <v>3.38</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,7 +9908,7 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AF48" t="n">
         <v>1.93</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>3.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="R52" t="n">
-        <v>2.21</v>
+        <v>3.31</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.38</v>
+        <v>1.99</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.65</v>
+        <v>3.22</v>
       </c>
       <c r="R53" t="n">
-        <v>7.85</v>
+        <v>3.94</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.98</v>
+        <v>1.72</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.22</v>
+        <v>3.84</v>
       </c>
       <c r="R55" t="n">
-        <v>3.94</v>
+        <v>4.18</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>6.33</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15627,10 +15627,10 @@
         <v>0</v>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH77" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="Q80" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="R80" t="n">
-        <v>4.81</v>
+        <v>2.27</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16218,10 +16218,10 @@
         <v>0</v>
       </c>
       <c r="AG80" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>3.01</v>
+        <v>1.9</v>
       </c>
       <c r="Q87" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="R87" t="n">
-        <v>2.52</v>
+        <v>3.7</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.49</v>
+        <v>2.33</v>
       </c>
       <c r="Q93" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="R93" t="n">
-        <v>5.45</v>
+        <v>3.12</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.33</v>
+        <v>2.08</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.1</v>
+        <v>3.74</v>
       </c>
       <c r="R94" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.08</v>
+        <v>1.49</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.74</v>
+        <v>4.7</v>
       </c>
       <c r="R95" t="n">
-        <v>3.13</v>
+        <v>5.45</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>1.83</v>
+        <v>7.75</v>
       </c>
       <c r="Q104" t="n">
-        <v>4</v>
+        <v>5.99</v>
       </c>
       <c r="R104" t="n">
-        <v>3.98</v>
+        <v>1.33</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>2.53</v>
+        <v>1.87</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.32</v>
+        <v>3.99</v>
       </c>
       <c r="R105" t="n">
-        <v>2.63</v>
+        <v>3.81</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21137,10 +21137,10 @@
         <v>0</v>
       </c>
       <c r="AE105" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF105" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>2.91</v>
+        <v>1.83</v>
       </c>
       <c r="Q106" t="n">
-        <v>2.97</v>
+        <v>4</v>
       </c>
       <c r="R106" t="n">
-        <v>2.56</v>
+        <v>3.98</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>7.75</v>
+        <v>2.91</v>
       </c>
       <c r="Q108" t="n">
-        <v>5.99</v>
+        <v>2.97</v>
       </c>
       <c r="R108" t="n">
-        <v>1.33</v>
+        <v>2.56</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1.87</v>
+        <v>2.53</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.99</v>
+        <v>3.32</v>
       </c>
       <c r="R111" t="n">
-        <v>3.81</v>
+        <v>2.63</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF111" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24486,10 +24486,10 @@
         <v>0</v>
       </c>
       <c r="AE122" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF122" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG122" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25077,10 +25077,10 @@
         <v>0</v>
       </c>
       <c r="AE125" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF125" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG125" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="Q128" t="n">
-        <v>3.48</v>
+        <v>4.97</v>
       </c>
       <c r="R128" t="n">
-        <v>2.14</v>
+        <v>9.9</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25668,10 +25668,10 @@
         <v>0</v>
       </c>
       <c r="AE128" t="n">
-        <v>1.66</v>
+        <v>1.93</v>
       </c>
       <c r="AF128" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AG128" t="n">
         <v>0</v>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="Q132" t="n">
-        <v>3.48</v>
+        <v>3.56</v>
       </c>
       <c r="R132" t="n">
-        <v>2.06</v>
+        <v>2.35</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="Q134" t="n">
-        <v>3.56</v>
+        <v>3.48</v>
       </c>
       <c r="R134" t="n">
-        <v>2.35</v>
+        <v>2.06</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27545,22 +27545,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27638,10 +27638,10 @@
         <v>0</v>
       </c>
       <c r="AE138" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF138" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG138" t="n">
         <v>0</v>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28032,10 +28032,10 @@
         <v>0</v>
       </c>
       <c r="AE140" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AF140" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG140" t="n">
         <v>0</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q144" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R144" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,10 +28972,10 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="Q145" t="n">
-        <v>3.1</v>
+        <v>3.58</v>
       </c>
       <c r="R145" t="n">
         <v>2.8</v>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q151" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R151" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q155" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R155" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -31288,22 +31288,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q157" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R157" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31381,10 +31381,10 @@
         <v>0</v>
       </c>
       <c r="AE157" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF157" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG157" t="n">
         <v>0</v>
@@ -31485,22 +31485,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,22 +31682,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,22 +31879,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q162" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R162" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32366,10 +32366,10 @@
         <v>0</v>
       </c>
       <c r="AE162" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF162" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG162" t="n">
         <v>0</v>

--- a/jogos_2026-04-06.xlsx
+++ b/jogos_2026-04-06.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI162"/>
+  <dimension ref="A1:BI163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.89</v>
+        <v>1.52</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.35</v>
+        <v>4.43</v>
       </c>
       <c r="R14" t="n">
-        <v>4.01</v>
+        <v>6.18</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.52</v>
+        <v>1.89</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.43</v>
+        <v>3.35</v>
       </c>
       <c r="R16" t="n">
-        <v>6.18</v>
+        <v>4.01</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>3.37</v>
+        <v>2.77</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.24</v>
+        <v>3.24</v>
       </c>
       <c r="R34" t="n">
-        <v>1.94</v>
+        <v>2.33</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.92</v>
+        <v>2.53</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.8</v>
+        <v>3.14</v>
       </c>
       <c r="R36" t="n">
-        <v>3.58</v>
+        <v>2.74</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.07</v>
+        <v>1.59</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.68</v>
+        <v>4.1</v>
       </c>
       <c r="R39" t="n">
-        <v>3.14</v>
+        <v>4.99</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.53</v>
+        <v>1.9</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="R41" t="n">
-        <v>2.74</v>
+        <v>3.4</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.42</v>
+        <v>3.36</v>
       </c>
       <c r="R46" t="n">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>7.85</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.02</v>
+        <v>3.38</v>
       </c>
       <c r="R48" t="n">
-        <v>3.38</v>
+        <v>3.31</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.38</v>
+        <v>3.84</v>
       </c>
       <c r="R52" t="n">
-        <v>3.31</v>
+        <v>4.18</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.99</v>
+        <v>1.38</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.22</v>
+        <v>4.65</v>
       </c>
       <c r="R53" t="n">
-        <v>3.94</v>
+        <v>7.85</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF53" t="n">
         <v>1.98</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>1.72</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.84</v>
+        <v>3.22</v>
       </c>
       <c r="R55" t="n">
-        <v>4.18</v>
+        <v>3.94</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.89</v>
+        <v>3.01</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R57" t="n">
-        <v>2.26</v>
+        <v>2.52</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.84</v>
+        <v>5.14</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="R61" t="n">
-        <v>2.35</v>
+        <v>1.6</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.02</v>
+        <v>2.31</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R64" t="n">
-        <v>3.35</v>
+        <v>2.92</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>4.04</v>
+        <v>1.8</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="R65" t="n">
-        <v>1.69</v>
+        <v>4.09</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>3.64</v>
+        <v>1.6</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="R66" t="n">
-        <v>1.92</v>
+        <v>4.81</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13460,10 +13460,10 @@
         <v>0</v>
       </c>
       <c r="AG66" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH66" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.75</v>
+        <v>2.41</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="R67" t="n">
-        <v>4.48</v>
+        <v>2.87</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.65</v>
+        <v>3.81</v>
       </c>
       <c r="R68" t="n">
-        <v>4.09</v>
+        <v>4.41</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.46</v>
+        <v>2.89</v>
       </c>
       <c r="Q69" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="R69" t="n">
-        <v>6.33</v>
+        <v>2.15</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>5.14</v>
+        <v>4.04</v>
       </c>
       <c r="Q70" t="n">
         <v>3.95</v>
       </c>
       <c r="R70" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>3.01</v>
+        <v>1.9</v>
       </c>
       <c r="Q71" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="R71" t="n">
-        <v>2.52</v>
+        <v>3.7</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.41</v>
+        <v>3.96</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R72" t="n">
-        <v>2.87</v>
+        <v>1.83</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2</v>
+        <v>2.84</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R74" t="n">
-        <v>3.56</v>
+        <v>2.35</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.65</v>
+        <v>1.88</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R76" t="n">
-        <v>2.39</v>
+        <v>4</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="Q77" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="R77" t="n">
-        <v>4.81</v>
+        <v>2.15</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15627,10 +15627,10 @@
         <v>0</v>
       </c>
       <c r="AG77" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.31</v>
+        <v>2.09</v>
       </c>
       <c r="Q79" t="n">
         <v>3.3</v>
       </c>
       <c r="R79" t="n">
-        <v>2.92</v>
+        <v>3.24</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R80" t="n">
-        <v>2.27</v>
+        <v>2.39</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.09</v>
+        <v>2.37</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R82" t="n">
-        <v>3.24</v>
+        <v>2.55</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>3.44</v>
+        <v>2.02</v>
       </c>
       <c r="Q83" t="n">
-        <v>2.99</v>
+        <v>3.35</v>
       </c>
       <c r="R83" t="n">
-        <v>2.37</v>
+        <v>3.35</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="R84" t="n">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1.9</v>
+        <v>1.46</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="R87" t="n">
-        <v>3.7</v>
+        <v>6.33</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.94</v>
+        <v>3.44</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="R88" t="n">
-        <v>2.24</v>
+        <v>2.37</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.88</v>
+        <v>2.94</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R89" t="n">
-        <v>3.81</v>
+        <v>2.24</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.99</v>
+        <v>1.88</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="R90" t="n">
-        <v>2.16</v>
+        <v>3.81</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="R91" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>7.75</v>
+        <v>4.25</v>
       </c>
       <c r="Q104" t="n">
-        <v>5.99</v>
+        <v>3.89</v>
       </c>
       <c r="R104" t="n">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.99</v>
+        <v>4</v>
       </c>
       <c r="R105" t="n">
-        <v>3.81</v>
+        <v>3.98</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1.83</v>
+        <v>7.75</v>
       </c>
       <c r="Q106" t="n">
-        <v>4</v>
+        <v>5.99</v>
       </c>
       <c r="R106" t="n">
-        <v>3.98</v>
+        <v>1.33</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.53</v>
+        <v>2.91</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.32</v>
+        <v>2.97</v>
       </c>
       <c r="R111" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF111" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22713,10 +22713,10 @@
         <v>0</v>
       </c>
       <c r="AE113" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF113" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG113" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q118" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="Q125" t="n">
-        <v>3.48</v>
+        <v>4.97</v>
       </c>
       <c r="R125" t="n">
-        <v>2.14</v>
+        <v>9.9</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25077,10 +25077,10 @@
         <v>0</v>
       </c>
       <c r="AE125" t="n">
-        <v>1.66</v>
+        <v>1.93</v>
       </c>
       <c r="AF125" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AG125" t="n">
         <v>0</v>
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="Q128" t="n">
-        <v>4.97</v>
+        <v>3.48</v>
       </c>
       <c r="R128" t="n">
-        <v>9.9</v>
+        <v>2.14</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25668,10 +25668,10 @@
         <v>0</v>
       </c>
       <c r="AE128" t="n">
-        <v>1.93</v>
+        <v>1.66</v>
       </c>
       <c r="AF128" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AG128" t="n">
         <v>0</v>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27047,10 +27047,10 @@
         <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF135" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG135" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>1.68</v>
+        <v>2.6</v>
       </c>
       <c r="Q137" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="R137" t="n">
-        <v>5.08</v>
+        <v>2.62</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27441,10 +27441,10 @@
         <v>0</v>
       </c>
       <c r="AE137" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF137" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>2.6</v>
+        <v>1.68</v>
       </c>
       <c r="Q138" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="R138" t="n">
-        <v>2.62</v>
+        <v>5.08</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27638,10 +27638,10 @@
         <v>0</v>
       </c>
       <c r="AE138" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AF138" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG138" t="n">
         <v>0</v>
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q139" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27835,10 +27835,10 @@
         <v>0</v>
       </c>
       <c r="AE139" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF139" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG139" t="n">
         <v>0</v>
@@ -27939,22 +27939,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>2.27</v>
+        <v>2.16</v>
       </c>
       <c r="Q142" t="n">
-        <v>2.9</v>
+        <v>3.58</v>
       </c>
       <c r="R142" t="n">
-        <v>3.55</v>
+        <v>2.8</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28574,137 +28574,137 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P143" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="Q143" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="R143" t="n">
-        <v>2.48</v>
+        <v>3.55</v>
       </c>
       <c r="S143" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T143" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U143" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="V143" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W143" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="X143" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Y143" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z143" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB143" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC143" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD143" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AE143" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF143" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AG143" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AH143" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI143" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="AJ143" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK143" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL143" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM143" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN143" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AO143" t="n">
         <v>0</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ143" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AR143" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AS143" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AT143" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AU143" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="AV143" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AW143" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AX143" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AY143" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ143" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BA143" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="BB143" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC143" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BD143" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE143" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BF143" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG143" t="n">
         <v>0</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28771,137 +28771,137 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P144" t="n">
         <v>2.5</v>
       </c>
       <c r="Q144" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R144" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S144" t="n">
         <v>3.1</v>
       </c>
-      <c r="R144" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="S144" t="n">
-        <v>0</v>
-      </c>
       <c r="T144" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U144" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V144" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W144" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="X144" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y144" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z144" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA144" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB144" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC144" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD144" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AE144" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF144" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG144" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AH144" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI144" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="AJ144" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK144" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL144" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM144" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN144" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO144" t="n">
         <v>0</v>
       </c>
       <c r="AP144" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ144" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR144" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS144" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AT144" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AU144" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="AV144" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AW144" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AX144" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY144" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ144" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BA144" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BB144" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC144" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD144" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE144" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF144" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG144" t="n">
         <v>0</v>
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,10 +28972,10 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="Q145" t="n">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="R145" t="n">
         <v>2.8</v>
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="Q155" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R155" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -31086,12 +31086,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>12.49</v>
+        <v>3.55</v>
       </c>
       <c r="Q156" t="n">
-        <v>6.92</v>
+        <v>3.7</v>
       </c>
       <c r="R156" t="n">
-        <v>1.2</v>
+        <v>1.92</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31184,10 +31184,10 @@
         <v>0</v>
       </c>
       <c r="AE156" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF156" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG156" t="n">
         <v>0</v>
@@ -31274,7 +31274,7 @@
         <v>0</v>
       </c>
       <c r="BI156" s="3" t="n">
-        <v>46118.69791666666</v>
+        <v>46118.66666666666</v>
       </c>
     </row>
     <row r="157">
@@ -31283,12 +31283,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>0</v>
+        <v>12.49</v>
       </c>
       <c r="Q157" t="n">
-        <v>0</v>
+        <v>6.92</v>
       </c>
       <c r="R157" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31381,10 +31381,10 @@
         <v>0</v>
       </c>
       <c r="AE157" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF157" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG157" t="n">
         <v>0</v>
@@ -31471,7 +31471,7 @@
         <v>0</v>
       </c>
       <c r="BI157" s="3" t="n">
-        <v>46118.875</v>
+        <v>46118.69791666666</v>
       </c>
     </row>
     <row r="158">
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,22 +31879,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31927,13 +31927,13 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q160" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R160" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
@@ -31972,10 +31972,10 @@
         <v>0</v>
       </c>
       <c r="AE160" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF160" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG160" t="n">
         <v>0</v>
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,22 +32273,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q162" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R162" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32366,10 +32366,10 @@
         <v>0</v>
       </c>
       <c r="AE162" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF162" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG162" t="n">
         <v>0</v>
@@ -32456,6 +32456,203 @@
         <v>0</v>
       </c>
       <c r="BI162" s="3" t="n">
+        <v>46118.875</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Greece Super League</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Atromitos</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Kifisia</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0</v>
+      </c>
+      <c r="I163" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" t="n">
+        <v>0</v>
+      </c>
+      <c r="L163" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N163" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>0</v>
+      </c>
+      <c r="R163" t="n">
+        <v>0</v>
+      </c>
+      <c r="S163" t="n">
+        <v>0</v>
+      </c>
+      <c r="T163" t="n">
+        <v>0</v>
+      </c>
+      <c r="U163" t="n">
+        <v>0</v>
+      </c>
+      <c r="V163" t="n">
+        <v>0</v>
+      </c>
+      <c r="W163" t="n">
+        <v>0</v>
+      </c>
+      <c r="X163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI163" s="3" t="n">
         <v>46118.875</v>
       </c>
     </row>

--- a/jogos_2026-04-06.xlsx
+++ b/jogos_2026-04-06.xlsx
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.52</v>
+        <v>1.89</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.43</v>
+        <v>3.35</v>
       </c>
       <c r="R14" t="n">
-        <v>6.18</v>
+        <v>4.01</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>6.18</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.19</v>
+        <v>2.53</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.75</v>
+        <v>3.14</v>
       </c>
       <c r="R29" t="n">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.53</v>
+        <v>1.59</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.14</v>
+        <v>4.1</v>
       </c>
       <c r="R36" t="n">
-        <v>2.74</v>
+        <v>4.99</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3.15</v>
+        <v>1.99</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.36</v>
+        <v>3.22</v>
       </c>
       <c r="R46" t="n">
-        <v>2.21</v>
+        <v>3.94</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="R48" t="n">
-        <v>3.31</v>
+        <v>2.21</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.24</v>
+        <v>1.38</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.02</v>
+        <v>4.65</v>
       </c>
       <c r="R49" t="n">
-        <v>3.38</v>
+        <v>7.85</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>4.08</v>
+        <v>2.24</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.42</v>
+        <v>3.02</v>
       </c>
       <c r="R50" t="n">
-        <v>1.89</v>
+        <v>3.38</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>7.85</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>3.01</v>
+        <v>3.64</v>
       </c>
       <c r="Q57" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="R57" t="n">
-        <v>2.52</v>
+        <v>1.92</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>3.06</v>
+        <v>1.6</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="R59" t="n">
-        <v>2.16</v>
+        <v>4.81</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12081,10 +12081,10 @@
         <v>0</v>
       </c>
       <c r="AG59" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH59" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2</v>
+        <v>2.84</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R60" t="n">
-        <v>3.56</v>
+        <v>2.35</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.75</v>
+        <v>4.04</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="R62" t="n">
-        <v>4.48</v>
+        <v>1.69</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>6.33</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R64" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.6</v>
+        <v>3.06</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="R66" t="n">
-        <v>4.81</v>
+        <v>2.16</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13460,10 +13460,10 @@
         <v>0</v>
       </c>
       <c r="AG66" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.41</v>
+        <v>2</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R67" t="n">
-        <v>2.87</v>
+        <v>3.56</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.81</v>
+        <v>3.65</v>
       </c>
       <c r="R68" t="n">
-        <v>4.41</v>
+        <v>4.09</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.89</v>
+        <v>3.44</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.55</v>
+        <v>2.99</v>
       </c>
       <c r="R69" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>4.04</v>
+        <v>3.1</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="R70" t="n">
-        <v>1.69</v>
+        <v>2.15</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.4</v>
+        <v>3.81</v>
       </c>
       <c r="R71" t="n">
-        <v>3.7</v>
+        <v>4.41</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>3.96</v>
+        <v>3.01</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="R72" t="n">
-        <v>1.83</v>
+        <v>2.52</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.84</v>
+        <v>2.65</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R74" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.89</v>
+        <v>2.09</v>
       </c>
       <c r="Q75" t="n">
         <v>3.3</v>
       </c>
       <c r="R75" t="n">
-        <v>2.26</v>
+        <v>3.24</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="Q77" t="n">
         <v>3.3</v>
       </c>
       <c r="R77" t="n">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.09</v>
+        <v>2.31</v>
       </c>
       <c r="Q79" t="n">
         <v>3.3</v>
       </c>
       <c r="R79" t="n">
-        <v>3.24</v>
+        <v>2.92</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R80" t="n">
-        <v>2.39</v>
+        <v>2.27</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.02</v>
+        <v>5.14</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="R83" t="n">
-        <v>3.35</v>
+        <v>1.6</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>3.64</v>
+        <v>2.65</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R86" t="n">
-        <v>1.92</v>
+        <v>2.36</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1.46</v>
+        <v>2.99</v>
       </c>
       <c r="Q87" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="R87" t="n">
-        <v>6.33</v>
+        <v>2.16</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>3.44</v>
+        <v>2.94</v>
       </c>
       <c r="Q88" t="n">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="R88" t="n">
-        <v>2.37</v>
+        <v>2.24</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.94</v>
+        <v>3.96</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R89" t="n">
-        <v>2.24</v>
+        <v>1.83</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18140,10 +18140,10 @@
         <v>1.88</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R90" t="n">
-        <v>3.81</v>
+        <v>4</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.99</v>
+        <v>2.02</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="R91" t="n">
-        <v>2.16</v>
+        <v>3.35</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.65</v>
+        <v>1.88</v>
       </c>
       <c r="Q92" t="n">
         <v>3.35</v>
       </c>
       <c r="R92" t="n">
-        <v>2.36</v>
+        <v>3.81</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.08</v>
+        <v>1.49</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.74</v>
+        <v>4.7</v>
       </c>
       <c r="R94" t="n">
-        <v>3.13</v>
+        <v>5.45</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>7.75</v>
+        <v>4.25</v>
       </c>
       <c r="Q106" t="n">
-        <v>5.99</v>
+        <v>3.89</v>
       </c>
       <c r="R106" t="n">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF110" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.91</v>
+        <v>7.75</v>
       </c>
       <c r="Q111" t="n">
-        <v>2.97</v>
+        <v>5.99</v>
       </c>
       <c r="R111" t="n">
-        <v>2.56</v>
+        <v>1.33</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22713,10 +22713,10 @@
         <v>0</v>
       </c>
       <c r="AE113" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF113" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG113" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24486,10 +24486,10 @@
         <v>0</v>
       </c>
       <c r="AE122" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF122" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG122" t="n">
         <v>0</v>
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24683,10 +24683,10 @@
         <v>0</v>
       </c>
       <c r="AE123" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF123" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG123" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25077,10 +25077,10 @@
         <v>0</v>
       </c>
       <c r="AE125" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF125" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG125" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,22 +25575,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25668,10 +25668,10 @@
         <v>0</v>
       </c>
       <c r="AE128" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF128" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG128" t="n">
         <v>0</v>
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.71</v>
+        <v>3.48</v>
       </c>
       <c r="R133" t="n">
-        <v>3.61</v>
+        <v>2.06</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="Q134" t="n">
-        <v>3.48</v>
+        <v>3.71</v>
       </c>
       <c r="R134" t="n">
-        <v>2.06</v>
+        <v>3.61</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q136" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R136" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27244,10 +27244,10 @@
         <v>0</v>
       </c>
       <c r="AE136" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF136" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG136" t="n">
         <v>0</v>
@@ -27348,22 +27348,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27441,10 +27441,10 @@
         <v>0</v>
       </c>
       <c r="AE137" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AF137" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG137" t="n">
         <v>0</v>
@@ -27939,22 +27939,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28377,137 +28377,137 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P142" t="n">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="Q142" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="R142" t="n">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="S142" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T142" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U142" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V142" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W142" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="X142" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y142" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z142" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA142" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB142" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC142" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD142" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AE142" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF142" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG142" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AH142" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI142" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="AJ142" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK142" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL142" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM142" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN142" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO142" t="n">
         <v>0</v>
       </c>
       <c r="AP142" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ142" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR142" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS142" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AT142" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AU142" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="AV142" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AW142" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AX142" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY142" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ142" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BA142" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BB142" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC142" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD142" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE142" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF142" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG142" t="n">
         <v>0</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28771,137 +28771,137 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P144" t="n">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="Q144" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="R144" t="n">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="S144" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T144" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U144" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="V144" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W144" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="X144" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Y144" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z144" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB144" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC144" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD144" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AE144" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF144" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AG144" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AH144" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI144" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="AJ144" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK144" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL144" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM144" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN144" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AO144" t="n">
         <v>0</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AR144" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AS144" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AT144" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AU144" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="AV144" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AW144" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AX144" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AY144" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ144" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BA144" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="BB144" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC144" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BD144" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE144" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BF144" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG144" t="n">
         <v>0</v>
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>1.94</v>
+        <v>2.62</v>
       </c>
       <c r="Q152" t="n">
-        <v>3.64</v>
+        <v>3.13</v>
       </c>
       <c r="R152" t="n">
-        <v>3.63</v>
+        <v>3.19</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30396,10 +30396,10 @@
         <v>0</v>
       </c>
       <c r="AE152" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AF152" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AG152" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>2.62</v>
+        <v>1.94</v>
       </c>
       <c r="Q153" t="n">
-        <v>3.13</v>
+        <v>3.64</v>
       </c>
       <c r="R153" t="n">
-        <v>3.19</v>
+        <v>3.63</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30593,10 +30593,10 @@
         <v>0</v>
       </c>
       <c r="AE153" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AF153" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AG153" t="n">
         <v>0</v>
@@ -31485,22 +31485,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,22 +31682,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -32076,22 +32076,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32470,22 +32470,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G163" t="n">

--- a/jogos_2026-04-06.xlsx
+++ b/jogos_2026-04-06.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>4.6</v>
+        <v>2.45</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.68</v>
+        <v>3.06</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.45</v>
+        <v>4.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.06</v>
+        <v>3.68</v>
       </c>
       <c r="R9" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.89</v>
+        <v>1.52</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.35</v>
+        <v>4.43</v>
       </c>
       <c r="R14" t="n">
-        <v>4.01</v>
+        <v>6.18</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.52</v>
+        <v>1.89</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.43</v>
+        <v>3.35</v>
       </c>
       <c r="R15" t="n">
-        <v>6.18</v>
+        <v>4.01</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.53</v>
+        <v>2.77</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.14</v>
+        <v>3.24</v>
       </c>
       <c r="R29" t="n">
-        <v>2.74</v>
+        <v>2.33</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.19</v>
+        <v>1.92</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="R32" t="n">
-        <v>2.85</v>
+        <v>3.58</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.59</v>
+        <v>2.07</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.1</v>
+        <v>3.68</v>
       </c>
       <c r="R36" t="n">
-        <v>4.99</v>
+        <v>3.14</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.77</v>
+        <v>1.9</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.24</v>
+        <v>3.6</v>
       </c>
       <c r="R40" t="n">
-        <v>2.33</v>
+        <v>3.4</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>4.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="R45" t="n">
-        <v>1.89</v>
+        <v>3.31</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.22</v>
+        <v>3.84</v>
       </c>
       <c r="R46" t="n">
-        <v>3.94</v>
+        <v>4.18</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.24</v>
+        <v>3.25</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.02</v>
+        <v>3.42</v>
       </c>
       <c r="R50" t="n">
-        <v>3.38</v>
+        <v>2.14</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,7 +10302,7 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AF50" t="n">
         <v>1.93</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>3.25</v>
+        <v>2.24</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.42</v>
+        <v>3.02</v>
       </c>
       <c r="R54" t="n">
-        <v>2.14</v>
+        <v>3.38</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,7 +11090,7 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AF54" t="n">
         <v>1.93</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>3.64</v>
+        <v>5.14</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="R57" t="n">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.6</v>
+        <v>3.44</v>
       </c>
       <c r="Q59" t="n">
-        <v>4.4</v>
+        <v>2.99</v>
       </c>
       <c r="R59" t="n">
-        <v>4.81</v>
+        <v>2.37</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12081,10 +12081,10 @@
         <v>0</v>
       </c>
       <c r="AG59" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.84</v>
+        <v>2.41</v>
       </c>
       <c r="Q60" t="n">
         <v>3.2</v>
       </c>
       <c r="R60" t="n">
-        <v>2.35</v>
+        <v>2.87</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>4.04</v>
+        <v>3.64</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="R62" t="n">
-        <v>1.69</v>
+        <v>1.92</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.46</v>
+        <v>1.88</v>
       </c>
       <c r="Q63" t="n">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="R63" t="n">
-        <v>6.33</v>
+        <v>4</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.41</v>
+        <v>1.9</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R64" t="n">
-        <v>2.87</v>
+        <v>3.7</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R67" t="n">
-        <v>3.56</v>
+        <v>3.35</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="R68" t="n">
-        <v>4.09</v>
+        <v>4.81</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13854,10 +13854,10 @@
         <v>0</v>
       </c>
       <c r="AG68" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH68" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>3.44</v>
+        <v>2.65</v>
       </c>
       <c r="Q69" t="n">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="R69" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="R70" t="n">
-        <v>2.15</v>
+        <v>4.09</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.79</v>
+        <v>3.06</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.81</v>
+        <v>3.55</v>
       </c>
       <c r="R71" t="n">
-        <v>4.41</v>
+        <v>2.16</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF71" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>3.01</v>
+        <v>2</v>
       </c>
       <c r="Q72" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="R72" t="n">
-        <v>2.52</v>
+        <v>3.56</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14988,10 +14988,10 @@
         <v>2.65</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="R74" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.89</v>
+        <v>3.96</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R77" t="n">
-        <v>2.26</v>
+        <v>1.83</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.31</v>
+        <v>4.04</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="R79" t="n">
-        <v>2.92</v>
+        <v>1.69</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.9</v>
+        <v>3.01</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R80" t="n">
-        <v>2.27</v>
+        <v>2.52</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="R81" t="n">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>5.14</v>
+        <v>2.09</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="R83" t="n">
-        <v>1.6</v>
+        <v>3.24</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="R87" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.94</v>
+        <v>1.79</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.3</v>
+        <v>3.81</v>
       </c>
       <c r="R88" t="n">
-        <v>2.24</v>
+        <v>4.41</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>3.96</v>
+        <v>2.99</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="R89" t="n">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.88</v>
+        <v>3.1</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R90" t="n">
-        <v>4</v>
+        <v>2.15</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="Q91" t="n">
         <v>3.35</v>
       </c>
       <c r="R91" t="n">
-        <v>3.35</v>
+        <v>3.81</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.88</v>
+        <v>1.46</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="R92" t="n">
-        <v>3.81</v>
+        <v>6.33</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.33</v>
+        <v>1.49</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="R93" t="n">
-        <v>3.12</v>
+        <v>5.45</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.49</v>
+        <v>2.33</v>
       </c>
       <c r="Q94" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="R94" t="n">
-        <v>5.45</v>
+        <v>3.12</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>2.91</v>
+        <v>7.75</v>
       </c>
       <c r="Q108" t="n">
-        <v>2.97</v>
+        <v>5.99</v>
       </c>
       <c r="R108" t="n">
-        <v>2.56</v>
+        <v>1.33</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1.87</v>
+        <v>2.91</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.99</v>
+        <v>2.97</v>
       </c>
       <c r="R109" t="n">
-        <v>3.81</v>
+        <v>2.56</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF110" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>7.75</v>
+        <v>2.53</v>
       </c>
       <c r="Q111" t="n">
-        <v>5.99</v>
+        <v>3.32</v>
       </c>
       <c r="R111" t="n">
-        <v>1.33</v>
+        <v>2.63</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF111" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>2.71</v>
+        <v>3.22</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.42</v>
+        <v>3</v>
       </c>
       <c r="R118" t="n">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24683,10 +24683,10 @@
         <v>0</v>
       </c>
       <c r="AE123" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF123" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG123" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,22 +25969,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q130" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R130" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26062,10 +26062,10 @@
         <v>0</v>
       </c>
       <c r="AE130" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF130" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG130" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.48</v>
+        <v>3.71</v>
       </c>
       <c r="R133" t="n">
-        <v>2.06</v>
+        <v>3.61</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="Q134" t="n">
-        <v>3.71</v>
+        <v>3.48</v>
       </c>
       <c r="R134" t="n">
-        <v>3.61</v>
+        <v>2.06</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27047,10 +27047,10 @@
         <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF135" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG135" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>2.6</v>
+        <v>1.68</v>
       </c>
       <c r="Q136" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="R136" t="n">
-        <v>2.62</v>
+        <v>5.08</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27244,10 +27244,10 @@
         <v>0</v>
       </c>
       <c r="AE136" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AF136" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG136" t="n">
         <v>0</v>
@@ -27348,22 +27348,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="Q138" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="R138" t="n">
-        <v>5.08</v>
+        <v>4.61</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27638,10 +27638,10 @@
         <v>0</v>
       </c>
       <c r="AE138" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF138" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG138" t="n">
         <v>0</v>
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28032,10 +28032,10 @@
         <v>0</v>
       </c>
       <c r="AE140" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF140" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG140" t="n">
         <v>0</v>
@@ -28377,7 +28377,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="Q143" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="R143" t="n">
-        <v>3.55</v>
+        <v>2.8</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="Q145" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="R145" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q154" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R154" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="Q156" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R156" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31485,22 +31485,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,22 +31682,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,22 +31879,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31927,13 +31927,13 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q160" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R160" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
@@ -31972,10 +31972,10 @@
         <v>0</v>
       </c>
       <c r="AE160" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF160" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG160" t="n">
         <v>0</v>
@@ -32076,22 +32076,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,22 +32273,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q162" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R162" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32366,10 +32366,10 @@
         <v>0</v>
       </c>
       <c r="AE162" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF162" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG162" t="n">
         <v>0</v>
@@ -32470,22 +32470,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G163" t="n">

--- a/jogos_2026-04-06.xlsx
+++ b/jogos_2026-04-06.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.52</v>
+        <v>1.89</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.43</v>
+        <v>3.35</v>
       </c>
       <c r="R14" t="n">
-        <v>6.18</v>
+        <v>4.01</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.89</v>
+        <v>1.52</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.35</v>
+        <v>4.43</v>
       </c>
       <c r="R15" t="n">
-        <v>4.01</v>
+        <v>6.18</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="R23" t="n">
-        <v>2.36</v>
+        <v>2.41</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.19</v>
+        <v>3.37</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.75</v>
+        <v>4.24</v>
       </c>
       <c r="R30" t="n">
-        <v>2.85</v>
+        <v>1.94</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.92</v>
+        <v>2.77</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.8</v>
+        <v>3.24</v>
       </c>
       <c r="R32" t="n">
-        <v>3.58</v>
+        <v>2.33</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>3.37</v>
+        <v>1.9</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.24</v>
+        <v>3.6</v>
       </c>
       <c r="R39" t="n">
-        <v>1.94</v>
+        <v>3.4</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.9</v>
+        <v>2.19</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="R40" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.1</v>
+        <v>3.25</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.38</v>
+        <v>3.42</v>
       </c>
       <c r="R45" t="n">
-        <v>3.31</v>
+        <v>2.14</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.75</v>
+        <v>4.08</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.84</v>
+        <v>3.42</v>
       </c>
       <c r="R46" t="n">
-        <v>4.18</v>
+        <v>1.89</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>3.25</v>
+        <v>2.24</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.42</v>
+        <v>3.02</v>
       </c>
       <c r="R50" t="n">
-        <v>2.14</v>
+        <v>3.38</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,7 +10302,7 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AF50" t="n">
         <v>1.93</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>5.14</v>
+        <v>3.06</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="R57" t="n">
-        <v>1.6</v>
+        <v>2.16</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>3.44</v>
+        <v>1.9</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.99</v>
+        <v>3.4</v>
       </c>
       <c r="R59" t="n">
-        <v>2.37</v>
+        <v>3.7</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R60" t="n">
-        <v>2.87</v>
+        <v>2.55</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.89</v>
+        <v>2.65</v>
       </c>
       <c r="Q61" t="n">
         <v>3.3</v>
       </c>
       <c r="R61" t="n">
-        <v>2.26</v>
+        <v>2.39</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>3.64</v>
+        <v>2.09</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R62" t="n">
-        <v>1.92</v>
+        <v>3.24</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.9</v>
+        <v>2.89</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R64" t="n">
-        <v>3.7</v>
+        <v>2.26</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R65" t="n">
-        <v>4.48</v>
+        <v>3.56</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.02</v>
+        <v>2.89</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="R67" t="n">
-        <v>3.35</v>
+        <v>2.15</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13854,10 +13854,10 @@
         <v>0</v>
       </c>
       <c r="AG68" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.65</v>
+        <v>1.75</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="R69" t="n">
-        <v>2.39</v>
+        <v>4.48</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.8</v>
+        <v>2.84</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="R70" t="n">
-        <v>4.09</v>
+        <v>2.35</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>3.06</v>
+        <v>4.04</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="R71" t="n">
-        <v>2.16</v>
+        <v>1.69</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.37</v>
+        <v>3.64</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R73" t="n">
-        <v>2.55</v>
+        <v>1.92</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.65</v>
+        <v>1.88</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R74" t="n">
-        <v>2.36</v>
+        <v>4</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>3.96</v>
+        <v>2.9</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R77" t="n">
-        <v>1.83</v>
+        <v>2.27</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.84</v>
+        <v>3.01</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R78" t="n">
-        <v>2.35</v>
+        <v>2.52</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>4.04</v>
+        <v>1.8</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="R79" t="n">
-        <v>1.69</v>
+        <v>4.09</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>3.01</v>
+        <v>5.14</v>
       </c>
       <c r="Q80" t="n">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="R80" t="n">
-        <v>2.52</v>
+        <v>1.6</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.9</v>
+        <v>2.41</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R81" t="n">
-        <v>2.27</v>
+        <v>2.87</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.09</v>
+        <v>3.1</v>
       </c>
       <c r="Q83" t="n">
         <v>3.3</v>
       </c>
       <c r="R83" t="n">
-        <v>3.24</v>
+        <v>2.15</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.89</v>
+        <v>2.31</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="R84" t="n">
-        <v>2.15</v>
+        <v>2.92</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.94</v>
+        <v>1.88</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="R87" t="n">
-        <v>2.24</v>
+        <v>3.81</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.79</v>
+        <v>2.99</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.81</v>
+        <v>3.45</v>
       </c>
       <c r="R88" t="n">
-        <v>4.41</v>
+        <v>2.16</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.99</v>
+        <v>2.65</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="R89" t="n">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>3.1</v>
+        <v>1.46</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="R90" t="n">
-        <v>2.15</v>
+        <v>6.33</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="R91" t="n">
-        <v>3.81</v>
+        <v>4.81</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18385,10 +18385,10 @@
         <v>0</v>
       </c>
       <c r="AG91" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH91" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>6.33</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.49</v>
+        <v>2.33</v>
       </c>
       <c r="Q93" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="R93" t="n">
-        <v>5.45</v>
+        <v>3.12</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="R94" t="n">
-        <v>3.12</v>
+        <v>2.74</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF94" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>1.87</v>
+        <v>7.75</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.99</v>
+        <v>5.99</v>
       </c>
       <c r="R104" t="n">
-        <v>3.81</v>
+        <v>1.33</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>4.25</v>
+        <v>2.53</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.89</v>
+        <v>3.32</v>
       </c>
       <c r="R106" t="n">
-        <v>1.8</v>
+        <v>2.63</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21334,10 +21334,10 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF106" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG106" t="n">
         <v>0</v>
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF111" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q120" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24092,10 +24092,10 @@
         <v>0</v>
       </c>
       <c r="AE120" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF120" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG120" t="n">
         <v>0</v>
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24486,10 +24486,10 @@
         <v>0</v>
       </c>
       <c r="AE122" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF122" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG122" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25274,10 +25274,10 @@
         <v>0</v>
       </c>
       <c r="AE126" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF126" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG126" t="n">
         <v>0</v>
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,22 +25969,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26062,10 +26062,10 @@
         <v>0</v>
       </c>
       <c r="AE130" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF130" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG130" t="n">
         <v>0</v>
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>3.24</v>
+        <v>2</v>
       </c>
       <c r="Q132" t="n">
-        <v>3.56</v>
+        <v>3.71</v>
       </c>
       <c r="R132" t="n">
-        <v>2.35</v>
+        <v>3.61</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>2</v>
+        <v>3.24</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.71</v>
+        <v>3.56</v>
       </c>
       <c r="R133" t="n">
-        <v>3.61</v>
+        <v>2.35</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27047,10 +27047,10 @@
         <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF135" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG135" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q136" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27545,22 +27545,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27638,10 +27638,10 @@
         <v>0</v>
       </c>
       <c r="AE138" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF138" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG138" t="n">
         <v>0</v>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28384,130 +28384,130 @@
         <v>2.5</v>
       </c>
       <c r="Q142" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R142" t="n">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="S142" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T142" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U142" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="V142" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W142" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="X142" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Y142" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z142" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB142" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC142" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD142" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AE142" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF142" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AG142" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AH142" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI142" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="AJ142" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK142" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL142" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM142" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN142" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AO142" t="n">
         <v>0</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ142" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AR142" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AS142" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AT142" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AU142" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="AV142" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AW142" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AX142" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AY142" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ142" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BA142" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="BB142" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC142" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BD142" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE142" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BF142" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG142" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="Q143" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="R143" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,133 +28972,133 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="Q145" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="R145" t="n">
-        <v>3.55</v>
+        <v>2.48</v>
       </c>
       <c r="S145" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T145" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U145" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V145" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W145" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="X145" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y145" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z145" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA145" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB145" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC145" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD145" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AE145" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF145" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG145" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AH145" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI145" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="AJ145" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK145" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL145" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM145" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN145" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO145" t="n">
         <v>0</v>
       </c>
       <c r="AP145" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ145" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR145" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS145" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AT145" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AU145" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="AV145" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AW145" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AX145" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY145" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ145" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BA145" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BB145" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC145" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD145" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE145" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF145" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG145" t="n">
         <v>0</v>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="Q154" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R154" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q156" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R156" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31485,22 +31485,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -32076,22 +32076,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,22 +32273,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q162" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R162" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32366,10 +32366,10 @@
         <v>0</v>
       </c>
       <c r="AE162" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF162" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG162" t="n">
         <v>0</v>
@@ -32470,22 +32470,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32518,13 +32518,13 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q163" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R163" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S163" t="n">
         <v>0</v>
@@ -32563,10 +32563,10 @@
         <v>0</v>
       </c>
       <c r="AE163" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF163" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG163" t="n">
         <v>0</v>

--- a/jogos_2026-04-06.xlsx
+++ b/jogos_2026-04-06.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>4.6</v>
+        <v>2.45</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.68</v>
+        <v>3.06</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.45</v>
+        <v>4.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.06</v>
+        <v>3.68</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.63</v>
+        <v>2.11</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="R20" t="n">
-        <v>4.69</v>
+        <v>3.21</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.53</v>
+        <v>3.37</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.14</v>
+        <v>4.24</v>
       </c>
       <c r="R35" t="n">
-        <v>2.74</v>
+        <v>1.94</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.9</v>
+        <v>2.77</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.6</v>
+        <v>3.24</v>
       </c>
       <c r="R39" t="n">
-        <v>3.4</v>
+        <v>2.33</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.19</v>
+        <v>1.92</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="R40" t="n">
-        <v>2.85</v>
+        <v>3.58</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="R41" t="n">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3.25</v>
+        <v>1.38</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.42</v>
+        <v>4.65</v>
       </c>
       <c r="R45" t="n">
-        <v>2.14</v>
+        <v>7.85</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>4.08</v>
+        <v>3.15</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.42</v>
+        <v>3.36</v>
       </c>
       <c r="R46" t="n">
-        <v>1.89</v>
+        <v>2.21</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3.15</v>
+        <v>4.08</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="R48" t="n">
-        <v>2.21</v>
+        <v>1.89</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.38</v>
+        <v>1.75</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.65</v>
+        <v>3.84</v>
       </c>
       <c r="R49" t="n">
-        <v>7.85</v>
+        <v>4.18</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.24</v>
+        <v>3.25</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.02</v>
+        <v>3.42</v>
       </c>
       <c r="R50" t="n">
-        <v>3.38</v>
+        <v>2.14</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,7 +10302,7 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AF50" t="n">
         <v>1.93</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>3.06</v>
+        <v>5.14</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="R57" t="n">
-        <v>2.16</v>
+        <v>1.6</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R61" t="n">
-        <v>2.39</v>
+        <v>2.27</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.09</v>
+        <v>3.96</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R62" t="n">
-        <v>3.24</v>
+        <v>1.83</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.89</v>
+        <v>1.8</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="R64" t="n">
-        <v>2.26</v>
+        <v>4.09</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2</v>
+        <v>2.94</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R65" t="n">
-        <v>3.56</v>
+        <v>2.24</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.94</v>
+        <v>2.41</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R66" t="n">
-        <v>2.24</v>
+        <v>2.87</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13609,10 +13609,10 @@
         <v>2.89</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="R67" t="n">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="R70" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>4.04</v>
+        <v>3.01</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="R71" t="n">
-        <v>1.69</v>
+        <v>2.52</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>3.64</v>
+        <v>1.46</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="R73" t="n">
-        <v>1.92</v>
+        <v>6.33</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.88</v>
+        <v>4.04</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="R74" t="n">
-        <v>4</v>
+        <v>1.69</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R75" t="n">
-        <v>3.35</v>
+        <v>3.24</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>3.01</v>
+        <v>2.65</v>
       </c>
       <c r="Q78" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="R78" t="n">
-        <v>2.52</v>
+        <v>2.36</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.8</v>
+        <v>3.44</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.65</v>
+        <v>2.99</v>
       </c>
       <c r="R79" t="n">
-        <v>4.09</v>
+        <v>2.37</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>5.14</v>
+        <v>1.88</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="R80" t="n">
-        <v>1.6</v>
+        <v>3.81</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.41</v>
+        <v>2.99</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="R81" t="n">
-        <v>2.87</v>
+        <v>2.16</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>3.44</v>
+        <v>2.02</v>
       </c>
       <c r="Q82" t="n">
-        <v>2.99</v>
+        <v>3.35</v>
       </c>
       <c r="R82" t="n">
-        <v>2.37</v>
+        <v>3.35</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17203,10 +17203,10 @@
         <v>0</v>
       </c>
       <c r="AG85" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH85" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.79</v>
+        <v>3.64</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.81</v>
+        <v>3.4</v>
       </c>
       <c r="R86" t="n">
-        <v>4.41</v>
+        <v>1.92</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R87" t="n">
-        <v>3.81</v>
+        <v>3.7</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.99</v>
+        <v>2.84</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="R88" t="n">
-        <v>2.16</v>
+        <v>2.35</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.65</v>
+        <v>3.06</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="R89" t="n">
-        <v>2.36</v>
+        <v>2.16</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>6.33</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="Q91" t="n">
-        <v>4.4</v>
+        <v>3.81</v>
       </c>
       <c r="R91" t="n">
-        <v>4.81</v>
+        <v>4.41</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,16 +18379,16 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG91" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH91" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.52</v>
+        <v>3.74</v>
       </c>
       <c r="R94" t="n">
-        <v>2.74</v>
+        <v>3.13</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF94" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.49</v>
+        <v>2.36</v>
       </c>
       <c r="Q95" t="n">
-        <v>4.7</v>
+        <v>3.52</v>
       </c>
       <c r="R95" t="n">
-        <v>5.45</v>
+        <v>2.74</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF95" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.08</v>
+        <v>1.49</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.74</v>
+        <v>4.7</v>
       </c>
       <c r="R96" t="n">
-        <v>3.13</v>
+        <v>5.45</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>2.53</v>
+        <v>1.83</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.32</v>
+        <v>4</v>
       </c>
       <c r="R106" t="n">
-        <v>2.63</v>
+        <v>3.98</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21334,10 +21334,10 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF106" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG106" t="n">
         <v>0</v>
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.91</v>
+        <v>2.53</v>
       </c>
       <c r="Q109" t="n">
-        <v>2.97</v>
+        <v>3.32</v>
       </c>
       <c r="R109" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF109" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.71</v>
+        <v>3.22</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.42</v>
+        <v>3</v>
       </c>
       <c r="R115" t="n">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="Q120" t="n">
-        <v>4.97</v>
+        <v>3.48</v>
       </c>
       <c r="R120" t="n">
-        <v>9.9</v>
+        <v>2.14</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24092,10 +24092,10 @@
         <v>0</v>
       </c>
       <c r="AE120" t="n">
-        <v>1.93</v>
+        <v>1.66</v>
       </c>
       <c r="AF120" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AG120" t="n">
         <v>0</v>
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24683,10 +24683,10 @@
         <v>0</v>
       </c>
       <c r="AE123" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF123" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG123" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25274,10 +25274,10 @@
         <v>0</v>
       </c>
       <c r="AE126" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF126" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG126" t="n">
         <v>0</v>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>2</v>
+        <v>3.24</v>
       </c>
       <c r="Q132" t="n">
-        <v>3.71</v>
+        <v>3.56</v>
       </c>
       <c r="R132" t="n">
-        <v>3.61</v>
+        <v>2.35</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>3.24</v>
+        <v>2</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.56</v>
+        <v>3.71</v>
       </c>
       <c r="R133" t="n">
-        <v>2.35</v>
+        <v>3.61</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27047,10 +27047,10 @@
         <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF135" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG135" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q136" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R136" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27244,10 +27244,10 @@
         <v>0</v>
       </c>
       <c r="AE136" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF136" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG136" t="n">
         <v>0</v>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27545,22 +27545,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q139" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R139" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27835,10 +27835,10 @@
         <v>0</v>
       </c>
       <c r="AE139" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF139" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG139" t="n">
         <v>0</v>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>2.6</v>
+        <v>1.68</v>
       </c>
       <c r="Q140" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="R140" t="n">
-        <v>2.62</v>
+        <v>5.08</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28032,10 +28032,10 @@
         <v>0</v>
       </c>
       <c r="AE140" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AF140" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG140" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,133 +28578,133 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="Q143" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="R143" t="n">
-        <v>3.55</v>
+        <v>2.48</v>
       </c>
       <c r="S143" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T143" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U143" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V143" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W143" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="X143" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y143" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z143" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA143" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB143" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC143" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD143" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AE143" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF143" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG143" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AH143" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI143" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="AJ143" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK143" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL143" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM143" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN143" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO143" t="n">
         <v>0</v>
       </c>
       <c r="AP143" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR143" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS143" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AT143" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AU143" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="AV143" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AW143" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AX143" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY143" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ143" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BA143" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BB143" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC143" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD143" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE143" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF143" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG143" t="n">
         <v>0</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>2.16</v>
+        <v>2.27</v>
       </c>
       <c r="Q144" t="n">
-        <v>3.58</v>
+        <v>2.9</v>
       </c>
       <c r="R144" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,133 +28972,133 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="Q145" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="R145" t="n">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="S145" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T145" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U145" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="V145" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W145" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="X145" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Y145" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z145" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB145" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC145" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD145" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AE145" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF145" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AG145" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AH145" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI145" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="AJ145" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK145" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL145" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM145" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN145" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AO145" t="n">
         <v>0</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ145" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AR145" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AS145" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AT145" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AU145" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="AV145" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AW145" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AX145" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AY145" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ145" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BA145" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="BB145" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC145" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BD145" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE145" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BF145" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG145" t="n">
         <v>0</v>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>2.62</v>
+        <v>1.94</v>
       </c>
       <c r="Q152" t="n">
-        <v>3.13</v>
+        <v>3.64</v>
       </c>
       <c r="R152" t="n">
-        <v>3.19</v>
+        <v>3.63</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30396,10 +30396,10 @@
         <v>0</v>
       </c>
       <c r="AE152" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AF152" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AG152" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>1.94</v>
+        <v>2.62</v>
       </c>
       <c r="Q153" t="n">
-        <v>3.64</v>
+        <v>3.13</v>
       </c>
       <c r="R153" t="n">
-        <v>3.63</v>
+        <v>3.19</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30593,10 +30593,10 @@
         <v>0</v>
       </c>
       <c r="AE153" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AF153" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AG153" t="n">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q155" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R155" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="Q156" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R156" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31485,22 +31485,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q158" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R158" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31578,10 +31578,10 @@
         <v>0</v>
       </c>
       <c r="AE158" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF158" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG158" t="n">
         <v>0</v>
@@ -31682,22 +31682,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32076,22 +32076,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,22 +32273,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32518,13 +32518,13 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q163" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R163" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S163" t="n">
         <v>0</v>
@@ -32563,10 +32563,10 @@
         <v>0</v>
       </c>
       <c r="AE163" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF163" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG163" t="n">
         <v>0</v>

--- a/jogos_2026-04-06.xlsx
+++ b/jogos_2026-04-06.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.45</v>
+        <v>4.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.06</v>
+        <v>3.68</v>
       </c>
       <c r="R9" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>4.6</v>
+        <v>2.45</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.68</v>
+        <v>3.06</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>6.18</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.89</v>
+        <v>1.52</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.35</v>
+        <v>4.43</v>
       </c>
       <c r="R16" t="n">
-        <v>4.01</v>
+        <v>6.18</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.63</v>
+        <v>2.28</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.15</v>
+        <v>3.64</v>
       </c>
       <c r="R17" t="n">
-        <v>4.69</v>
+        <v>2.83</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.11</v>
+        <v>2.74</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="R20" t="n">
-        <v>3.21</v>
+        <v>2.41</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.74</v>
+        <v>2.11</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="R28" t="n">
-        <v>2.41</v>
+        <v>3.21</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.53</v>
+        <v>1.9</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="R36" t="n">
-        <v>2.74</v>
+        <v>3.4</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.92</v>
+        <v>3.37</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.8</v>
+        <v>4.24</v>
       </c>
       <c r="R40" t="n">
-        <v>3.58</v>
+        <v>1.94</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="R41" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.38</v>
+        <v>3.25</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.65</v>
+        <v>3.42</v>
       </c>
       <c r="R45" t="n">
-        <v>7.85</v>
+        <v>2.14</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3.15</v>
+        <v>4.04</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.36</v>
+        <v>3.75</v>
       </c>
       <c r="R46" t="n">
-        <v>2.21</v>
+        <v>1.73</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.84</v>
+        <v>3.22</v>
       </c>
       <c r="R49" t="n">
-        <v>4.18</v>
+        <v>3.94</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>3.25</v>
+        <v>2.24</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.42</v>
+        <v>3.02</v>
       </c>
       <c r="R50" t="n">
-        <v>2.14</v>
+        <v>3.38</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,7 +10302,7 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AF50" t="n">
         <v>1.93</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.24</v>
+        <v>3.15</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.02</v>
+        <v>3.36</v>
       </c>
       <c r="R52" t="n">
-        <v>3.38</v>
+        <v>2.21</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.38</v>
+        <v>3.84</v>
       </c>
       <c r="R55" t="n">
-        <v>3.31</v>
+        <v>4.18</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>5.14</v>
+        <v>3.64</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="R57" t="n">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.9</v>
+        <v>2.31</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R61" t="n">
-        <v>2.27</v>
+        <v>2.92</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.65</v>
+        <v>3.81</v>
       </c>
       <c r="R64" t="n">
-        <v>4.09</v>
+        <v>4.41</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.94</v>
+        <v>1.8</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="R65" t="n">
-        <v>2.24</v>
+        <v>4.09</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.41</v>
+        <v>5.14</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="R66" t="n">
-        <v>2.87</v>
+        <v>1.6</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.88</v>
+        <v>1.46</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="R68" t="n">
-        <v>4</v>
+        <v>6.33</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.75</v>
+        <v>2.41</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="R69" t="n">
-        <v>4.48</v>
+        <v>2.87</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.89</v>
+        <v>1.75</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="R70" t="n">
-        <v>2.15</v>
+        <v>4.48</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>3.01</v>
+        <v>1.9</v>
       </c>
       <c r="Q71" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="R71" t="n">
-        <v>2.52</v>
+        <v>3.7</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.37</v>
+        <v>2.65</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="R72" t="n">
-        <v>2.55</v>
+        <v>2.36</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.46</v>
+        <v>3.06</v>
       </c>
       <c r="Q73" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="R73" t="n">
-        <v>6.33</v>
+        <v>2.16</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>4.04</v>
+        <v>3.96</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="R74" t="n">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.09</v>
+        <v>2.89</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="R75" t="n">
-        <v>3.24</v>
+        <v>2.15</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R76" t="n">
-        <v>3.56</v>
+        <v>4</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.65</v>
+        <v>2</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R78" t="n">
-        <v>2.36</v>
+        <v>3.56</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>3.44</v>
+        <v>2.02</v>
       </c>
       <c r="Q79" t="n">
-        <v>2.99</v>
+        <v>3.35</v>
       </c>
       <c r="R79" t="n">
-        <v>2.37</v>
+        <v>3.35</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="R80" t="n">
-        <v>3.81</v>
+        <v>4.81</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16218,10 +16218,10 @@
         <v>0</v>
       </c>
       <c r="AG80" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH80" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="R81" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.31</v>
+        <v>1.88</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="R84" t="n">
-        <v>2.92</v>
+        <v>3.81</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1.6</v>
+        <v>2.65</v>
       </c>
       <c r="Q85" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="R85" t="n">
-        <v>4.81</v>
+        <v>2.39</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17203,10 +17203,10 @@
         <v>0</v>
       </c>
       <c r="AG85" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH85" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1.9</v>
+        <v>3.44</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.4</v>
+        <v>2.99</v>
       </c>
       <c r="R87" t="n">
-        <v>3.7</v>
+        <v>2.37</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.84</v>
+        <v>2.37</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R88" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="R89" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.79</v>
+        <v>2.9</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.81</v>
+        <v>3.25</v>
       </c>
       <c r="R91" t="n">
-        <v>4.41</v>
+        <v>2.27</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.65</v>
+        <v>3.01</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R92" t="n">
-        <v>2.39</v>
+        <v>2.52</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="R93" t="n">
-        <v>3.12</v>
+        <v>2.74</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF93" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.08</v>
+        <v>2.33</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.74</v>
+        <v>3.1</v>
       </c>
       <c r="R94" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.36</v>
+        <v>1.49</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.52</v>
+        <v>4.7</v>
       </c>
       <c r="R95" t="n">
-        <v>2.74</v>
+        <v>5.45</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF95" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.49</v>
+        <v>2.08</v>
       </c>
       <c r="Q96" t="n">
-        <v>4.7</v>
+        <v>3.74</v>
       </c>
       <c r="R96" t="n">
-        <v>5.45</v>
+        <v>3.13</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>7.75</v>
+        <v>2.91</v>
       </c>
       <c r="Q104" t="n">
-        <v>5.99</v>
+        <v>2.97</v>
       </c>
       <c r="R104" t="n">
-        <v>1.33</v>
+        <v>2.56</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1.87</v>
+        <v>7.75</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.99</v>
+        <v>5.99</v>
       </c>
       <c r="R107" t="n">
-        <v>3.81</v>
+        <v>1.33</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF109" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22713,10 +22713,10 @@
         <v>0</v>
       </c>
       <c r="AE113" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF113" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG113" t="n">
         <v>0</v>
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q120" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24092,10 +24092,10 @@
         <v>0</v>
       </c>
       <c r="AE120" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF120" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG120" t="n">
         <v>0</v>
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24683,10 +24683,10 @@
         <v>0</v>
       </c>
       <c r="AE123" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF123" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG123" t="n">
         <v>0</v>
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25077,10 +25077,10 @@
         <v>0</v>
       </c>
       <c r="AE125" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF125" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG125" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,22 +25969,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q130" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R130" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26062,10 +26062,10 @@
         <v>0</v>
       </c>
       <c r="AE130" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF130" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG130" t="n">
         <v>0</v>
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="Q132" t="n">
-        <v>3.56</v>
+        <v>3.48</v>
       </c>
       <c r="R132" t="n">
-        <v>2.35</v>
+        <v>2.06</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>2</v>
+        <v>3.24</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.71</v>
+        <v>3.56</v>
       </c>
       <c r="R133" t="n">
-        <v>3.61</v>
+        <v>2.35</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="Q134" t="n">
-        <v>3.48</v>
+        <v>3.71</v>
       </c>
       <c r="R134" t="n">
-        <v>2.06</v>
+        <v>3.61</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27047,10 +27047,10 @@
         <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF135" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG135" t="n">
         <v>0</v>
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>2.6</v>
+        <v>1.77</v>
       </c>
       <c r="Q136" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="R136" t="n">
-        <v>2.62</v>
+        <v>4.61</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27244,10 +27244,10 @@
         <v>0</v>
       </c>
       <c r="AE136" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="AF136" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AG136" t="n">
         <v>0</v>
@@ -27348,22 +27348,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q139" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27835,10 +27835,10 @@
         <v>0</v>
       </c>
       <c r="AE139" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF139" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG139" t="n">
         <v>0</v>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,10 +28381,10 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="Q142" t="n">
-        <v>3.1</v>
+        <v>3.58</v>
       </c>
       <c r="R142" t="n">
         <v>2.8</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="Q144" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="R144" t="n">
-        <v>3.55</v>
+        <v>2.8</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>2.16</v>
+        <v>2.27</v>
       </c>
       <c r="Q145" t="n">
-        <v>3.58</v>
+        <v>2.9</v>
       </c>
       <c r="R145" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>1.94</v>
+        <v>2.62</v>
       </c>
       <c r="Q152" t="n">
-        <v>3.64</v>
+        <v>3.13</v>
       </c>
       <c r="R152" t="n">
-        <v>3.63</v>
+        <v>3.19</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30396,10 +30396,10 @@
         <v>0</v>
       </c>
       <c r="AE152" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AF152" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AG152" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>2.62</v>
+        <v>1.94</v>
       </c>
       <c r="Q153" t="n">
-        <v>3.13</v>
+        <v>3.64</v>
       </c>
       <c r="R153" t="n">
-        <v>3.19</v>
+        <v>3.63</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30593,10 +30593,10 @@
         <v>0</v>
       </c>
       <c r="AE153" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AF153" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AG153" t="n">
         <v>0</v>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q158" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R158" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31578,10 +31578,10 @@
         <v>0</v>
       </c>
       <c r="AE158" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF158" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG158" t="n">
         <v>0</v>
@@ -32076,22 +32076,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q161" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R161" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32169,10 +32169,10 @@
         <v>0</v>
       </c>
       <c r="AE161" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF161" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG161" t="n">
         <v>0</v>
@@ -32470,22 +32470,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G163" t="n">

--- a/jogos_2026-04-06.xlsx
+++ b/jogos_2026-04-06.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.95</v>
+        <v>7.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.68</v>
+        <v>5.4</v>
       </c>
       <c r="R12" t="n">
-        <v>3.47</v>
+        <v>1.28</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>7.8</v>
+        <v>1.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.4</v>
+        <v>3.68</v>
       </c>
       <c r="R13" t="n">
-        <v>1.28</v>
+        <v>3.47</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.89</v>
+        <v>1.52</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.35</v>
+        <v>4.43</v>
       </c>
       <c r="R14" t="n">
-        <v>4.01</v>
+        <v>6.18</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>6.18</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.28</v>
+        <v>2.74</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.64</v>
+        <v>3.42</v>
       </c>
       <c r="R17" t="n">
-        <v>2.83</v>
+        <v>2.41</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.74</v>
+        <v>2.11</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="R20" t="n">
-        <v>2.41</v>
+        <v>3.21</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6116,83 +6116,83 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.19</v>
+        <v>1.92</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="R29" t="n">
-        <v>2.85</v>
+        <v>3.58</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
@@ -6234,19 +6234,19 @@
         <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.59</v>
+        <v>1.9</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="R32" t="n">
-        <v>4.99</v>
+        <v>3.4</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.77</v>
+        <v>2.07</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.24</v>
+        <v>3.68</v>
       </c>
       <c r="R39" t="n">
-        <v>2.33</v>
+        <v>3.14</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.92</v>
+        <v>3.37</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.8</v>
+        <v>4.24</v>
       </c>
       <c r="R41" t="n">
-        <v>3.58</v>
+        <v>1.94</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>4.04</v>
+        <v>4.08</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="R46" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.24</v>
+        <v>1.38</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.02</v>
+        <v>4.65</v>
       </c>
       <c r="R50" t="n">
-        <v>3.38</v>
+        <v>7.85</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.38</v>
+        <v>3.84</v>
       </c>
       <c r="R51" t="n">
-        <v>3.31</v>
+        <v>4.18</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>3.15</v>
+        <v>4.04</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.36</v>
+        <v>3.75</v>
       </c>
       <c r="R52" t="n">
-        <v>2.21</v>
+        <v>1.73</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.38</v>
+        <v>3.25</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.65</v>
+        <v>3.42</v>
       </c>
       <c r="R54" t="n">
-        <v>7.85</v>
+        <v>2.14</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.75</v>
+        <v>2.24</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.84</v>
+        <v>3.02</v>
       </c>
       <c r="R55" t="n">
-        <v>4.18</v>
+        <v>3.38</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.89</v>
+        <v>2.31</v>
       </c>
       <c r="Q58" t="n">
         <v>3.3</v>
       </c>
       <c r="R58" t="n">
-        <v>2.26</v>
+        <v>2.92</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>4.04</v>
+        <v>1.75</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="R60" t="n">
-        <v>1.69</v>
+        <v>4.48</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R61" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.81</v>
+        <v>3.65</v>
       </c>
       <c r="R64" t="n">
-        <v>4.41</v>
+        <v>4.09</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1.8</v>
+        <v>2.37</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="R65" t="n">
-        <v>4.09</v>
+        <v>2.55</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>5.14</v>
+        <v>2</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="R66" t="n">
-        <v>1.6</v>
+        <v>3.56</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.46</v>
+        <v>1.79</v>
       </c>
       <c r="Q68" t="n">
-        <v>4.1</v>
+        <v>3.81</v>
       </c>
       <c r="R68" t="n">
-        <v>6.33</v>
+        <v>4.41</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.41</v>
+        <v>1.6</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="R69" t="n">
-        <v>2.87</v>
+        <v>4.81</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14051,10 +14051,10 @@
         <v>0</v>
       </c>
       <c r="AG69" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH69" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.75</v>
+        <v>4.04</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="R70" t="n">
-        <v>4.48</v>
+        <v>1.69</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.9</v>
+        <v>2.89</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R71" t="n">
-        <v>3.7</v>
+        <v>2.26</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.65</v>
+        <v>2.02</v>
       </c>
       <c r="Q72" t="n">
         <v>3.35</v>
       </c>
       <c r="R72" t="n">
-        <v>2.36</v>
+        <v>3.35</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>3.06</v>
+        <v>1.9</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="R73" t="n">
-        <v>2.16</v>
+        <v>3.7</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>3.96</v>
+        <v>2.99</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="R74" t="n">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.89</v>
+        <v>1.46</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="R75" t="n">
-        <v>2.15</v>
+        <v>6.33</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.88</v>
+        <v>2.65</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R76" t="n">
-        <v>4</v>
+        <v>2.36</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.84</v>
+        <v>1.88</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="R77" t="n">
-        <v>2.35</v>
+        <v>3.81</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2</v>
+        <v>2.65</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R78" t="n">
-        <v>3.56</v>
+        <v>2.39</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R79" t="n">
-        <v>3.35</v>
+        <v>3.24</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="Q80" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="R80" t="n">
-        <v>4.81</v>
+        <v>2.27</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16218,10 +16218,10 @@
         <v>0</v>
       </c>
       <c r="AG80" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="Q81" t="n">
         <v>3.3</v>
       </c>
       <c r="R81" t="n">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.09</v>
+        <v>2.84</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R83" t="n">
-        <v>3.24</v>
+        <v>2.35</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1.88</v>
+        <v>3.44</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.35</v>
+        <v>2.99</v>
       </c>
       <c r="R84" t="n">
-        <v>3.81</v>
+        <v>2.37</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.37</v>
+        <v>3.01</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="R88" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>3.1</v>
+        <v>3.64</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R89" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="R91" t="n">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>3.01</v>
+        <v>2.94</v>
       </c>
       <c r="Q92" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R92" t="n">
-        <v>2.52</v>
+        <v>2.24</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.52</v>
+        <v>3.1</v>
       </c>
       <c r="R93" t="n">
-        <v>2.74</v>
+        <v>3.12</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF93" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.33</v>
+        <v>2.08</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.1</v>
+        <v>3.74</v>
       </c>
       <c r="R94" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.08</v>
+        <v>2.36</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.74</v>
+        <v>3.52</v>
       </c>
       <c r="R96" t="n">
-        <v>3.13</v>
+        <v>2.74</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>7.75</v>
+        <v>1.87</v>
       </c>
       <c r="Q107" t="n">
-        <v>5.99</v>
+        <v>3.99</v>
       </c>
       <c r="R107" t="n">
-        <v>1.33</v>
+        <v>3.81</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1.83</v>
+        <v>2.91</v>
       </c>
       <c r="Q112" t="n">
-        <v>4</v>
+        <v>2.97</v>
       </c>
       <c r="R112" t="n">
-        <v>3.98</v>
+        <v>2.56</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>3.22</v>
+        <v>2.71</v>
       </c>
       <c r="Q115" t="n">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="R115" t="n">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q120" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24092,10 +24092,10 @@
         <v>0</v>
       </c>
       <c r="AE120" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF120" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG120" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25077,10 +25077,10 @@
         <v>0</v>
       </c>
       <c r="AE125" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF125" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG125" t="n">
         <v>0</v>
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25471,10 +25471,10 @@
         <v>0</v>
       </c>
       <c r="AE127" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF127" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG127" t="n">
         <v>0</v>
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,22 +25969,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26062,10 +26062,10 @@
         <v>0</v>
       </c>
       <c r="AE130" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF130" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG130" t="n">
         <v>0</v>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27047,10 +27047,10 @@
         <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AF135" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG135" t="n">
         <v>0</v>
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1.77</v>
+        <v>2.6</v>
       </c>
       <c r="Q136" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="R136" t="n">
-        <v>4.61</v>
+        <v>2.62</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27244,10 +27244,10 @@
         <v>0</v>
       </c>
       <c r="AE136" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="AF136" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AG136" t="n">
         <v>0</v>
@@ -27348,22 +27348,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27638,10 +27638,10 @@
         <v>0</v>
       </c>
       <c r="AE138" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF138" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG138" t="n">
         <v>0</v>
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q139" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R139" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27939,22 +27939,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,10 +28381,10 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="Q142" t="n">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="R142" t="n">
         <v>2.8</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,10 +28775,10 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="Q144" t="n">
-        <v>3.1</v>
+        <v>3.58</v>
       </c>
       <c r="R144" t="n">
         <v>2.8</v>
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="Q155" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R155" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q156" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R156" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32076,22 +32076,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q161" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R161" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32169,10 +32169,10 @@
         <v>0</v>
       </c>
       <c r="AE161" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF161" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG161" t="n">
         <v>0</v>
@@ -32470,22 +32470,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32518,13 +32518,13 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q163" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R163" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S163" t="n">
         <v>0</v>
@@ -32563,10 +32563,10 @@
         <v>0</v>
       </c>
       <c r="AE163" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF163" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG163" t="n">
         <v>0</v>

--- a/jogos_2026-04-06.xlsx
+++ b/jogos_2026-04-06.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI163"/>
+  <dimension ref="A1:BI160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>4.6</v>
+        <v>2.21</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.68</v>
+        <v>3.05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9</v>
+        <v>3.11</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>7.8</v>
+        <v>1.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.4</v>
+        <v>3.68</v>
       </c>
       <c r="R12" t="n">
-        <v>1.28</v>
+        <v>3.47</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.95</v>
+        <v>7.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.68</v>
+        <v>5.4</v>
       </c>
       <c r="R13" t="n">
-        <v>3.47</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.52</v>
+        <v>1.89</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.43</v>
+        <v>3.35</v>
       </c>
       <c r="R14" t="n">
-        <v>6.18</v>
+        <v>4.01</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.89</v>
+        <v>1.52</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.35</v>
+        <v>4.43</v>
       </c>
       <c r="R15" t="n">
-        <v>4.01</v>
+        <v>6.18</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.11</v>
+        <v>2.28</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="R20" t="n">
-        <v>3.21</v>
+        <v>2.83</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.84</v>
+        <v>2.11</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="R21" t="n">
-        <v>2.36</v>
+        <v>3.21</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6116,83 +6116,83 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.92</v>
+        <v>3.37</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.8</v>
+        <v>4.24</v>
       </c>
       <c r="R29" t="n">
-        <v>3.58</v>
+        <v>1.94</v>
       </c>
       <c r="S29" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
@@ -6234,19 +6234,19 @@
         <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.19</v>
+        <v>1.33</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="R30" t="n">
-        <v>2.85</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.9</v>
+        <v>2.77</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.6</v>
+        <v>3.24</v>
       </c>
       <c r="R32" t="n">
-        <v>3.4</v>
+        <v>2.33</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.53</v>
+        <v>1.59</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.14</v>
+        <v>4.1</v>
       </c>
       <c r="R33" t="n">
-        <v>2.74</v>
+        <v>4.99</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.77</v>
+        <v>2.07</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.24</v>
+        <v>3.68</v>
       </c>
       <c r="R35" t="n">
-        <v>2.33</v>
+        <v>3.14</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7889,83 +7889,83 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
@@ -8007,19 +8007,19 @@
         <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.07</v>
+        <v>3.01</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.68</v>
+        <v>3.2</v>
       </c>
       <c r="R39" t="n">
-        <v>3.14</v>
+        <v>2.19</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.37</v>
+        <v>1.9</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.24</v>
+        <v>3.6</v>
       </c>
       <c r="R41" t="n">
-        <v>1.94</v>
+        <v>3.4</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.59</v>
+        <v>3.15</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.1</v>
+        <v>3.16</v>
       </c>
       <c r="R43" t="n">
-        <v>4.99</v>
+        <v>2.14</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>4.08</v>
+        <v>1.38</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.42</v>
+        <v>4.65</v>
       </c>
       <c r="R46" t="n">
-        <v>1.89</v>
+        <v>7.85</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.38</v>
+        <v>3.84</v>
       </c>
       <c r="R48" t="n">
-        <v>3.31</v>
+        <v>4.18</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.99</v>
+        <v>2.24</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.22</v>
+        <v>3.02</v>
       </c>
       <c r="R49" t="n">
-        <v>3.94</v>
+        <v>3.38</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.98</v>
+        <v>1.76</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.72</v>
+        <v>1.93</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.38</v>
+        <v>3.25</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.65</v>
+        <v>3.42</v>
       </c>
       <c r="R50" t="n">
-        <v>7.85</v>
+        <v>2.14</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.75</v>
+        <v>4.08</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.84</v>
+        <v>3.42</v>
       </c>
       <c r="R51" t="n">
-        <v>4.18</v>
+        <v>1.89</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>4.04</v>
+        <v>2.1</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.75</v>
+        <v>3.38</v>
       </c>
       <c r="R52" t="n">
-        <v>1.73</v>
+        <v>3.31</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>3.25</v>
+        <v>4.04</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="R54" t="n">
-        <v>2.14</v>
+        <v>1.73</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.24</v>
+        <v>5.08</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="R55" t="n">
-        <v>3.38</v>
+        <v>1.77</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.31</v>
+        <v>2.89</v>
       </c>
       <c r="Q58" t="n">
         <v>3.3</v>
       </c>
       <c r="R58" t="n">
-        <v>2.92</v>
+        <v>2.26</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.41</v>
+        <v>3.96</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R61" t="n">
-        <v>2.87</v>
+        <v>1.83</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>5.14</v>
+        <v>2.84</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="R62" t="n">
-        <v>1.6</v>
+        <v>2.35</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.8</v>
+        <v>2.09</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="R64" t="n">
-        <v>4.09</v>
+        <v>3.24</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.37</v>
+        <v>2.89</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="R65" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="R66" t="n">
-        <v>3.56</v>
+        <v>4.09</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>6.33</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.79</v>
+        <v>3.1</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.81</v>
+        <v>3.3</v>
       </c>
       <c r="R68" t="n">
-        <v>4.41</v>
+        <v>2.15</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14051,10 +14051,10 @@
         <v>0</v>
       </c>
       <c r="AG69" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH69" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>4.04</v>
+        <v>3.01</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="R70" t="n">
-        <v>1.69</v>
+        <v>2.52</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.89</v>
+        <v>2.31</v>
       </c>
       <c r="Q71" t="n">
         <v>3.3</v>
       </c>
       <c r="R71" t="n">
-        <v>2.26</v>
+        <v>2.92</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.02</v>
+        <v>2.9</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R72" t="n">
-        <v>3.35</v>
+        <v>2.27</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.9</v>
+        <v>2.99</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="R73" t="n">
-        <v>3.7</v>
+        <v>2.16</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.99</v>
+        <v>2.65</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="R74" t="n">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.46</v>
+        <v>1.88</v>
       </c>
       <c r="Q75" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="R75" t="n">
-        <v>6.33</v>
+        <v>3.81</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.65</v>
+        <v>1.6</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="R76" t="n">
-        <v>2.36</v>
+        <v>4.81</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15430,10 +15430,10 @@
         <v>0</v>
       </c>
       <c r="AG76" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH76" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.88</v>
+        <v>2.65</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R77" t="n">
-        <v>3.81</v>
+        <v>2.39</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.65</v>
+        <v>2.37</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R78" t="n">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="R79" t="n">
-        <v>3.24</v>
+        <v>3.35</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.9</v>
+        <v>1.88</v>
       </c>
       <c r="Q80" t="n">
         <v>3.25</v>
       </c>
       <c r="R80" t="n">
-        <v>2.27</v>
+        <v>4</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>3.1</v>
+        <v>3.64</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R81" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.88</v>
+        <v>2.41</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R82" t="n">
-        <v>4</v>
+        <v>2.87</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.84</v>
+        <v>1.75</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="R83" t="n">
-        <v>2.35</v>
+        <v>4.48</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>3.44</v>
+        <v>2.94</v>
       </c>
       <c r="Q84" t="n">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="R84" t="n">
-        <v>2.37</v>
+        <v>2.24</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>3.96</v>
+        <v>4.04</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="R86" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>3.64</v>
+        <v>3.06</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="R89" t="n">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.89</v>
+        <v>3.44</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.55</v>
+        <v>2.99</v>
       </c>
       <c r="R91" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.94</v>
+        <v>2</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R92" t="n">
-        <v>2.24</v>
+        <v>3.56</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.08</v>
+        <v>1.49</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.74</v>
+        <v>4.7</v>
       </c>
       <c r="R94" t="n">
-        <v>3.13</v>
+        <v>5.45</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.49</v>
+        <v>2.36</v>
       </c>
       <c r="Q95" t="n">
-        <v>4.7</v>
+        <v>3.52</v>
       </c>
       <c r="R95" t="n">
-        <v>5.45</v>
+        <v>2.74</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF95" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.52</v>
+        <v>3.74</v>
       </c>
       <c r="R96" t="n">
-        <v>2.74</v>
+        <v>3.13</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1.83</v>
+        <v>7.75</v>
       </c>
       <c r="Q105" t="n">
-        <v>4</v>
+        <v>5.99</v>
       </c>
       <c r="R105" t="n">
-        <v>3.98</v>
+        <v>1.33</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF111" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22713,10 +22713,10 @@
         <v>0</v>
       </c>
       <c r="AE113" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF113" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG113" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.71</v>
+        <v>2</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.42</v>
+        <v>3.02</v>
       </c>
       <c r="R115" t="n">
-        <v>2.39</v>
+        <v>3.71</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>3.22</v>
+        <v>2.71</v>
       </c>
       <c r="Q116" t="n">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="R116" t="n">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q118" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q120" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24092,10 +24092,10 @@
         <v>0</v>
       </c>
       <c r="AE120" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF120" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG120" t="n">
         <v>0</v>
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24486,10 +24486,10 @@
         <v>0</v>
       </c>
       <c r="AE122" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF122" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG122" t="n">
         <v>0</v>
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24683,10 +24683,10 @@
         <v>0</v>
       </c>
       <c r="AE123" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF123" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG123" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25471,10 +25471,10 @@
         <v>0</v>
       </c>
       <c r="AE127" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF127" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG127" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="Q132" t="n">
-        <v>3.48</v>
+        <v>3.71</v>
       </c>
       <c r="R132" t="n">
-        <v>2.06</v>
+        <v>3.61</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.56</v>
+        <v>3.48</v>
       </c>
       <c r="R133" t="n">
-        <v>2.35</v>
+        <v>2.06</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>2</v>
+        <v>3.24</v>
       </c>
       <c r="Q134" t="n">
-        <v>3.71</v>
+        <v>3.56</v>
       </c>
       <c r="R134" t="n">
-        <v>3.61</v>
+        <v>2.35</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>2.6</v>
+        <v>1.77</v>
       </c>
       <c r="Q136" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="R136" t="n">
-        <v>2.62</v>
+        <v>4.61</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27244,10 +27244,10 @@
         <v>0</v>
       </c>
       <c r="AE136" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="AF136" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AG136" t="n">
         <v>0</v>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27441,10 +27441,10 @@
         <v>0</v>
       </c>
       <c r="AE137" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF137" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27638,10 +27638,10 @@
         <v>0</v>
       </c>
       <c r="AE138" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF138" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG138" t="n">
         <v>0</v>
@@ -27939,22 +27939,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28384,130 +28384,130 @@
         <v>2.5</v>
       </c>
       <c r="Q142" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R142" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S142" t="n">
         <v>3.1</v>
       </c>
-      <c r="R142" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="S142" t="n">
-        <v>0</v>
-      </c>
       <c r="T142" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U142" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V142" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W142" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="X142" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y142" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z142" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA142" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB142" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC142" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD142" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AE142" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF142" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG142" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AH142" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI142" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="AJ142" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK142" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL142" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM142" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN142" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO142" t="n">
         <v>0</v>
       </c>
       <c r="AP142" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ142" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR142" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS142" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AT142" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AU142" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="AV142" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AW142" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AX142" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY142" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ142" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BA142" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BB142" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC142" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD142" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE142" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF142" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG142" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,133 +28578,133 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="Q143" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="R143" t="n">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="S143" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T143" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U143" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="V143" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W143" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="X143" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Y143" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z143" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB143" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC143" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD143" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AE143" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF143" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AG143" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AH143" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI143" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="AJ143" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK143" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL143" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM143" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN143" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AO143" t="n">
         <v>0</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ143" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AR143" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AS143" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AT143" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AU143" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="AV143" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AW143" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AX143" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AY143" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ143" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BA143" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="BB143" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC143" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BD143" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE143" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BF143" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG143" t="n">
         <v>0</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>2.16</v>
+        <v>2.27</v>
       </c>
       <c r="Q144" t="n">
-        <v>3.58</v>
+        <v>2.9</v>
       </c>
       <c r="R144" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="Q145" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="R145" t="n">
-        <v>3.55</v>
+        <v>2.8</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>2.62</v>
+        <v>1.94</v>
       </c>
       <c r="Q152" t="n">
-        <v>3.13</v>
+        <v>3.64</v>
       </c>
       <c r="R152" t="n">
-        <v>3.19</v>
+        <v>3.63</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30396,10 +30396,10 @@
         <v>0</v>
       </c>
       <c r="AE152" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AF152" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AG152" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>1.94</v>
+        <v>2.62</v>
       </c>
       <c r="Q153" t="n">
-        <v>3.64</v>
+        <v>3.13</v>
       </c>
       <c r="R153" t="n">
-        <v>3.63</v>
+        <v>3.19</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30593,10 +30593,10 @@
         <v>0</v>
       </c>
       <c r="AE153" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AF153" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AG153" t="n">
         <v>0</v>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q154" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R154" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="Q156" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R156" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,22 +31682,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,22 +31879,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31927,13 +31927,13 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q160" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R160" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
@@ -31972,10 +31972,10 @@
         <v>0</v>
       </c>
       <c r="AE160" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF160" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG160" t="n">
         <v>0</v>
@@ -32062,597 +32062,6 @@
         <v>0</v>
       </c>
       <c r="BI160" s="3" t="n">
-        <v>46118.875</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="n">
-        <v>46118</v>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Greece Super League</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Larissa</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>Panaitolikos</t>
-        </is>
-      </c>
-      <c r="G161" t="n">
-        <v>0</v>
-      </c>
-      <c r="H161" t="n">
-        <v>0</v>
-      </c>
-      <c r="I161" t="n">
-        <v>0</v>
-      </c>
-      <c r="J161" t="n">
-        <v>0</v>
-      </c>
-      <c r="K161" t="n">
-        <v>0</v>
-      </c>
-      <c r="L161" t="n">
-        <v>0</v>
-      </c>
-      <c r="M161" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N161" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O161" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P161" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
-      <c r="R161" t="n">
-        <v>0</v>
-      </c>
-      <c r="S161" t="n">
-        <v>0</v>
-      </c>
-      <c r="T161" t="n">
-        <v>0</v>
-      </c>
-      <c r="U161" t="n">
-        <v>0</v>
-      </c>
-      <c r="V161" t="n">
-        <v>0</v>
-      </c>
-      <c r="W161" t="n">
-        <v>0</v>
-      </c>
-      <c r="X161" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y161" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ161" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA161" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB161" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC161" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD161" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE161" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF161" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG161" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH161" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI161" s="3" t="n">
-        <v>46118.875</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="n">
-        <v>46118</v>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Goiás</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>Criciúma</t>
-        </is>
-      </c>
-      <c r="G162" t="n">
-        <v>0</v>
-      </c>
-      <c r="H162" t="n">
-        <v>0</v>
-      </c>
-      <c r="I162" t="n">
-        <v>0</v>
-      </c>
-      <c r="J162" t="n">
-        <v>0</v>
-      </c>
-      <c r="K162" t="n">
-        <v>0</v>
-      </c>
-      <c r="L162" t="n">
-        <v>0</v>
-      </c>
-      <c r="M162" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N162" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O162" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P162" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
-      <c r="R162" t="n">
-        <v>0</v>
-      </c>
-      <c r="S162" t="n">
-        <v>0</v>
-      </c>
-      <c r="T162" t="n">
-        <v>0</v>
-      </c>
-      <c r="U162" t="n">
-        <v>0</v>
-      </c>
-      <c r="V162" t="n">
-        <v>0</v>
-      </c>
-      <c r="W162" t="n">
-        <v>0</v>
-      </c>
-      <c r="X162" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y162" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ162" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA162" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB162" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC162" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD162" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE162" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF162" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG162" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH162" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI162" s="3" t="n">
-        <v>46118.875</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="n">
-        <v>46118</v>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Ecuador Primera Categoría Serie A</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>Libertad</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>Mushuc Runa SC</t>
-        </is>
-      </c>
-      <c r="G163" t="n">
-        <v>0</v>
-      </c>
-      <c r="H163" t="n">
-        <v>0</v>
-      </c>
-      <c r="I163" t="n">
-        <v>0</v>
-      </c>
-      <c r="J163" t="n">
-        <v>0</v>
-      </c>
-      <c r="K163" t="n">
-        <v>0</v>
-      </c>
-      <c r="L163" t="n">
-        <v>0</v>
-      </c>
-      <c r="M163" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N163" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O163" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P163" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="Q163" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="R163" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="S163" t="n">
-        <v>0</v>
-      </c>
-      <c r="T163" t="n">
-        <v>0</v>
-      </c>
-      <c r="U163" t="n">
-        <v>0</v>
-      </c>
-      <c r="V163" t="n">
-        <v>0</v>
-      </c>
-      <c r="W163" t="n">
-        <v>0</v>
-      </c>
-      <c r="X163" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y163" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE163" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF163" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ163" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA163" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB163" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC163" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD163" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE163" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF163" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG163" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH163" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI163" s="3" t="n">
         <v>46118.875</v>
       </c>
     </row>

--- a/jogos_2026-04-06.xlsx
+++ b/jogos_2026-04-06.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.21</v>
+        <v>3.96</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.05</v>
+        <v>3.38</v>
       </c>
       <c r="R8" t="n">
-        <v>3.11</v>
+        <v>1.81</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.96</v>
+        <v>4.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.38</v>
+        <v>3.68</v>
       </c>
       <c r="R9" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>4.6</v>
+        <v>2.21</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.68</v>
+        <v>3.05</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9</v>
+        <v>3.11</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.89</v>
+        <v>1.52</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.35</v>
+        <v>4.43</v>
       </c>
       <c r="R14" t="n">
-        <v>4.01</v>
+        <v>6.18</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>6.18</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.84</v>
+        <v>2.11</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="R27" t="n">
-        <v>2.36</v>
+        <v>3.21</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>3.37</v>
+        <v>1.59</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.24</v>
+        <v>4.1</v>
       </c>
       <c r="R29" t="n">
-        <v>1.94</v>
+        <v>4.99</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.33</v>
+        <v>2.07</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.1</v>
+        <v>3.68</v>
       </c>
       <c r="R30" t="n">
-        <v>9.449999999999999</v>
+        <v>3.14</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="R31" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.77</v>
+        <v>2.19</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.24</v>
+        <v>3.75</v>
       </c>
       <c r="R32" t="n">
-        <v>2.33</v>
+        <v>2.85</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.59</v>
+        <v>2.53</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.1</v>
+        <v>3.14</v>
       </c>
       <c r="R33" t="n">
-        <v>4.99</v>
+        <v>2.74</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7101,83 +7101,83 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="Q34" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R34" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W34" t="n">
         <v>3.28</v>
       </c>
-      <c r="R34" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7219,19 +7219,19 @@
         <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.07</v>
+        <v>1.67</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="R35" t="n">
-        <v>3.14</v>
+        <v>4.95</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.67</v>
+        <v>3.15</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.34</v>
+        <v>3.16</v>
       </c>
       <c r="R36" t="n">
-        <v>4.95</v>
+        <v>2.14</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7889,83 +7889,83 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="R38" t="n">
-        <v>3.58</v>
+        <v>5.05</v>
       </c>
       <c r="S38" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
@@ -8007,19 +8007,19 @@
         <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="R41" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.53</v>
+        <v>3.37</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.14</v>
+        <v>4.24</v>
       </c>
       <c r="R42" t="n">
-        <v>2.74</v>
+        <v>1.94</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>3.15</v>
+        <v>2.77</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.16</v>
+        <v>3.24</v>
       </c>
       <c r="R43" t="n">
-        <v>2.14</v>
+        <v>2.33</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.38</v>
+        <v>5.08</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.65</v>
+        <v>3.2</v>
       </c>
       <c r="R46" t="n">
-        <v>7.85</v>
+        <v>1.77</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.99</v>
+        <v>2.24</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.22</v>
+        <v>3.02</v>
       </c>
       <c r="R47" t="n">
-        <v>3.94</v>
+        <v>3.38</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.98</v>
+        <v>1.76</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.72</v>
+        <v>1.93</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.75</v>
+        <v>3.25</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.84</v>
+        <v>3.42</v>
       </c>
       <c r="R48" t="n">
-        <v>4.18</v>
+        <v>2.14</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.02</v>
+        <v>3.38</v>
       </c>
       <c r="R49" t="n">
-        <v>3.38</v>
+        <v>3.31</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>3.25</v>
+        <v>4.04</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="R50" t="n">
-        <v>2.14</v>
+        <v>1.73</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>4.08</v>
+        <v>1.75</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.42</v>
+        <v>3.84</v>
       </c>
       <c r="R51" t="n">
-        <v>1.89</v>
+        <v>4.18</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.1</v>
+        <v>1.38</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.38</v>
+        <v>4.65</v>
       </c>
       <c r="R52" t="n">
-        <v>3.31</v>
+        <v>7.85</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>3.15</v>
+        <v>4.08</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="R53" t="n">
-        <v>2.21</v>
+        <v>1.89</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>4.04</v>
+        <v>3.15</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.75</v>
+        <v>3.36</v>
       </c>
       <c r="R54" t="n">
-        <v>1.73</v>
+        <v>2.21</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.89</v>
+        <v>3.44</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="R58" t="n">
-        <v>2.26</v>
+        <v>2.37</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>5.14</v>
+        <v>2.37</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="R59" t="n">
-        <v>1.6</v>
+        <v>2.55</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.84</v>
+        <v>3.64</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R62" t="n">
-        <v>2.35</v>
+        <v>1.92</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.09</v>
+        <v>1.6</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="R64" t="n">
-        <v>3.24</v>
+        <v>4.81</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13066,10 +13066,10 @@
         <v>0</v>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.89</v>
+        <v>2.09</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="R65" t="n">
-        <v>2.15</v>
+        <v>3.24</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.8</v>
+        <v>2.65</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="R66" t="n">
-        <v>4.09</v>
+        <v>2.39</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>6.33</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="Q68" t="n">
         <v>3.3</v>
       </c>
       <c r="R68" t="n">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.31</v>
+        <v>2.94</v>
       </c>
       <c r="Q71" t="n">
         <v>3.3</v>
       </c>
       <c r="R71" t="n">
-        <v>2.92</v>
+        <v>2.24</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.9</v>
+        <v>1.79</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.25</v>
+        <v>3.81</v>
       </c>
       <c r="R72" t="n">
-        <v>2.27</v>
+        <v>4.41</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.99</v>
+        <v>5.14</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="R73" t="n">
-        <v>2.16</v>
+        <v>1.6</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="R75" t="n">
-        <v>3.81</v>
+        <v>4.09</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.6</v>
+        <v>2.89</v>
       </c>
       <c r="Q76" t="n">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="R76" t="n">
-        <v>4.81</v>
+        <v>2.15</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15430,10 +15430,10 @@
         <v>0</v>
       </c>
       <c r="AG76" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="Q77" t="n">
         <v>3.3</v>
       </c>
       <c r="R77" t="n">
-        <v>2.39</v>
+        <v>2.15</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R78" t="n">
-        <v>2.55</v>
+        <v>2.92</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.02</v>
+        <v>2.41</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="R79" t="n">
-        <v>3.35</v>
+        <v>2.87</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.88</v>
+        <v>3.01</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R80" t="n">
-        <v>4</v>
+        <v>2.52</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>3.64</v>
+        <v>2.9</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R81" t="n">
-        <v>1.92</v>
+        <v>2.27</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.41</v>
+        <v>1.75</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="R82" t="n">
-        <v>2.87</v>
+        <v>4.48</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.94</v>
+        <v>1.88</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="R84" t="n">
-        <v>2.24</v>
+        <v>3.81</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF85" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>4.04</v>
+        <v>3.96</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="R86" t="n">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>3.06</v>
+        <v>1.46</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="R89" t="n">
-        <v>2.16</v>
+        <v>6.33</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.9</v>
+        <v>3.06</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="R90" t="n">
-        <v>3.7</v>
+        <v>2.16</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>3.44</v>
+        <v>2.84</v>
       </c>
       <c r="Q91" t="n">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="R91" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="Q92" t="n">
         <v>3.4</v>
       </c>
       <c r="R92" t="n">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>7.75</v>
+        <v>1.87</v>
       </c>
       <c r="Q105" t="n">
-        <v>5.99</v>
+        <v>3.99</v>
       </c>
       <c r="R105" t="n">
-        <v>1.33</v>
+        <v>3.81</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21531,10 +21531,10 @@
         <v>0</v>
       </c>
       <c r="AE107" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF107" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG107" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2.91</v>
+        <v>7.75</v>
       </c>
       <c r="Q110" t="n">
-        <v>2.97</v>
+        <v>5.99</v>
       </c>
       <c r="R110" t="n">
-        <v>2.56</v>
+        <v>1.33</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.53</v>
+        <v>2.91</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.32</v>
+        <v>2.97</v>
       </c>
       <c r="R111" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF111" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2</v>
+        <v>2.71</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.02</v>
+        <v>3.42</v>
       </c>
       <c r="R115" t="n">
-        <v>3.71</v>
+        <v>2.39</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>2.71</v>
+        <v>3.22</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.42</v>
+        <v>3</v>
       </c>
       <c r="R116" t="n">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>3.22</v>
+        <v>3.27</v>
       </c>
       <c r="Q117" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R117" t="n">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>3.27</v>
+        <v>2</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="R118" t="n">
-        <v>2.08</v>
+        <v>3.71</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24486,10 +24486,10 @@
         <v>0</v>
       </c>
       <c r="AE122" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF122" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG122" t="n">
         <v>0</v>
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24683,10 +24683,10 @@
         <v>0</v>
       </c>
       <c r="AE123" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF123" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG123" t="n">
         <v>0</v>
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24880,10 +24880,10 @@
         <v>0</v>
       </c>
       <c r="AE124" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF124" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG124" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,22 +25575,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q128" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25668,10 +25668,10 @@
         <v>0</v>
       </c>
       <c r="AE128" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF128" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG128" t="n">
         <v>0</v>
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>2</v>
+        <v>3.24</v>
       </c>
       <c r="Q132" t="n">
-        <v>3.71</v>
+        <v>3.56</v>
       </c>
       <c r="R132" t="n">
-        <v>3.61</v>
+        <v>2.35</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>3.24</v>
+        <v>2</v>
       </c>
       <c r="Q134" t="n">
-        <v>3.56</v>
+        <v>3.71</v>
       </c>
       <c r="R134" t="n">
-        <v>2.35</v>
+        <v>3.61</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27047,10 +27047,10 @@
         <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF135" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG135" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q136" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27244,10 +27244,10 @@
         <v>0</v>
       </c>
       <c r="AE136" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF136" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG136" t="n">
         <v>0</v>
@@ -27348,22 +27348,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27441,10 +27441,10 @@
         <v>0</v>
       </c>
       <c r="AE137" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AF137" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28032,10 +28032,10 @@
         <v>0</v>
       </c>
       <c r="AE140" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF140" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG140" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>2.16</v>
+        <v>2.27</v>
       </c>
       <c r="Q143" t="n">
-        <v>3.58</v>
+        <v>2.9</v>
       </c>
       <c r="R143" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>2.27</v>
+        <v>2.16</v>
       </c>
       <c r="Q144" t="n">
-        <v>2.9</v>
+        <v>3.58</v>
       </c>
       <c r="R144" t="n">
-        <v>3.55</v>
+        <v>2.8</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="Q154" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R154" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q156" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R156" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31730,13 +31730,13 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q159" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R159" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S159" t="n">
         <v>0</v>
@@ -31775,10 +31775,10 @@
         <v>0</v>
       </c>
       <c r="AE159" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF159" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG159" t="n">
         <v>0</v>
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31927,13 +31927,13 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q160" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R160" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
@@ -31972,10 +31972,10 @@
         <v>0</v>
       </c>
       <c r="AE160" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF160" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG160" t="n">
         <v>0</v>

--- a/jogos_2026-04-06.xlsx
+++ b/jogos_2026-04-06.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI160"/>
+  <dimension ref="A1:BI159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>4.6</v>
+        <v>2.21</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.68</v>
+        <v>3.05</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9</v>
+        <v>3.11</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.21</v>
+        <v>4.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.05</v>
+        <v>3.68</v>
       </c>
       <c r="R10" t="n">
-        <v>3.11</v>
+        <v>1.9</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>6.18</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>6.18</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.63</v>
+        <v>2.84</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.15</v>
+        <v>3.44</v>
       </c>
       <c r="R18" t="n">
-        <v>4.69</v>
+        <v>2.36</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.28</v>
+        <v>2.11</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="R19" t="n">
-        <v>2.83</v>
+        <v>3.21</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.59</v>
+        <v>2.05</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.1</v>
+        <v>3.38</v>
       </c>
       <c r="R29" t="n">
-        <v>4.99</v>
+        <v>3.15</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.07</v>
+        <v>1.59</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.68</v>
+        <v>4.1</v>
       </c>
       <c r="R30" t="n">
-        <v>3.14</v>
+        <v>4.99</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="R31" t="n">
-        <v>3.4</v>
+        <v>5.05</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.19</v>
+        <v>3.37</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.75</v>
+        <v>4.24</v>
       </c>
       <c r="R32" t="n">
-        <v>2.85</v>
+        <v>1.94</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7101,83 +7101,83 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.92</v>
+        <v>2.53</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.8</v>
+        <v>3.14</v>
       </c>
       <c r="R34" t="n">
-        <v>3.58</v>
+        <v>2.74</v>
       </c>
       <c r="S34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7219,19 +7219,19 @@
         <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.67</v>
+        <v>3.15</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.34</v>
+        <v>3.16</v>
       </c>
       <c r="R35" t="n">
-        <v>4.95</v>
+        <v>2.14</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>3.15</v>
+        <v>2.07</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.16</v>
+        <v>3.68</v>
       </c>
       <c r="R36" t="n">
-        <v>2.14</v>
+        <v>3.14</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.33</v>
+        <v>2.19</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="R37" t="n">
-        <v>9.449999999999999</v>
+        <v>2.85</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7889,83 +7889,83 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="Q38" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R38" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U38" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W38" t="n">
         <v>3.28</v>
       </c>
-      <c r="R38" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
@@ -8007,19 +8007,19 @@
         <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>3.01</v>
+        <v>2.77</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="R39" t="n">
-        <v>2.19</v>
+        <v>2.33</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.05</v>
+        <v>1.33</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.38</v>
+        <v>4.1</v>
       </c>
       <c r="R41" t="n">
-        <v>3.15</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.37</v>
+        <v>1.9</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.24</v>
+        <v>3.6</v>
       </c>
       <c r="R42" t="n">
-        <v>1.94</v>
+        <v>3.4</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.77</v>
+        <v>3.01</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="R43" t="n">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.99</v>
+        <v>4.08</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.22</v>
+        <v>3.42</v>
       </c>
       <c r="R45" t="n">
-        <v>3.94</v>
+        <v>1.89</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>5.08</v>
+        <v>1.99</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="R46" t="n">
-        <v>1.77</v>
+        <v>3.94</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.24</v>
+        <v>3.15</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.02</v>
+        <v>3.36</v>
       </c>
       <c r="R47" t="n">
-        <v>3.38</v>
+        <v>2.21</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3.25</v>
+        <v>1.38</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.42</v>
+        <v>4.65</v>
       </c>
       <c r="R48" t="n">
-        <v>2.14</v>
+        <v>7.85</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.1</v>
+        <v>4.04</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.38</v>
+        <v>3.75</v>
       </c>
       <c r="R49" t="n">
-        <v>3.31</v>
+        <v>1.73</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>4.04</v>
+        <v>2.1</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.75</v>
+        <v>3.38</v>
       </c>
       <c r="R50" t="n">
-        <v>1.73</v>
+        <v>3.31</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.38</v>
+        <v>5.08</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.65</v>
+        <v>3.2</v>
       </c>
       <c r="R52" t="n">
-        <v>7.85</v>
+        <v>1.77</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>4.08</v>
+        <v>2.24</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.42</v>
+        <v>3.02</v>
       </c>
       <c r="R53" t="n">
-        <v>1.89</v>
+        <v>3.38</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="R54" t="n">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.99</v>
+        <v>2.31</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="R57" t="n">
-        <v>2.16</v>
+        <v>2.92</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>3.44</v>
+        <v>1.79</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.99</v>
+        <v>3.81</v>
       </c>
       <c r="R58" t="n">
-        <v>2.37</v>
+        <v>4.41</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.37</v>
+        <v>5.14</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="R59" t="n">
-        <v>2.55</v>
+        <v>1.6</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>3.64</v>
+        <v>1.88</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R62" t="n">
-        <v>1.92</v>
+        <v>3.81</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>4.04</v>
+        <v>1.88</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="R63" t="n">
-        <v>1.69</v>
+        <v>4</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="R65" t="n">
-        <v>3.24</v>
+        <v>3.35</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>6.33</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.89</v>
+        <v>2.41</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R68" t="n">
-        <v>2.26</v>
+        <v>2.87</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.88</v>
+        <v>2.99</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="R69" t="n">
-        <v>4</v>
+        <v>2.16</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.94</v>
+        <v>2.37</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R71" t="n">
-        <v>2.24</v>
+        <v>2.55</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.79</v>
+        <v>4.04</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.81</v>
+        <v>3.95</v>
       </c>
       <c r="R72" t="n">
-        <v>4.41</v>
+        <v>1.69</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>5.14</v>
+        <v>3.64</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="R73" t="n">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.8</v>
+        <v>2.84</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="R75" t="n">
-        <v>4.09</v>
+        <v>2.35</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.89</v>
+        <v>1.75</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="R76" t="n">
-        <v>2.15</v>
+        <v>4.48</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="R77" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.41</v>
+        <v>2.89</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="R79" t="n">
-        <v>2.87</v>
+        <v>2.15</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.9</v>
+        <v>3.96</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R81" t="n">
-        <v>2.27</v>
+        <v>1.83</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1.88</v>
+        <v>2.65</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R84" t="n">
-        <v>3.81</v>
+        <v>2.39</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>3.96</v>
+        <v>2.89</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R86" t="n">
-        <v>1.83</v>
+        <v>2.26</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="Q87" t="n">
         <v>3.4</v>
       </c>
       <c r="R87" t="n">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.02</v>
+        <v>2.94</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R88" t="n">
-        <v>3.35</v>
+        <v>2.24</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>6.33</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>3.06</v>
+        <v>2.9</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="R90" t="n">
-        <v>2.16</v>
+        <v>2.27</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R92" t="n">
-        <v>3.7</v>
+        <v>2.15</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.52</v>
+        <v>3.74</v>
       </c>
       <c r="R95" t="n">
-        <v>2.74</v>
+        <v>3.13</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF95" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.08</v>
+        <v>2.36</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.74</v>
+        <v>3.52</v>
       </c>
       <c r="R96" t="n">
-        <v>3.13</v>
+        <v>2.74</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.99</v>
+        <v>4</v>
       </c>
       <c r="R105" t="n">
-        <v>3.81</v>
+        <v>3.98</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="Q106" t="n">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="R106" t="n">
-        <v>3.98</v>
+        <v>3.81</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.71</v>
+        <v>3.27</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="R115" t="n">
-        <v>2.39</v>
+        <v>2.08</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>3.27</v>
+        <v>2.71</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="R117" t="n">
-        <v>2.08</v>
+        <v>2.39</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="Q124" t="n">
-        <v>4.97</v>
+        <v>3.48</v>
       </c>
       <c r="R124" t="n">
-        <v>9.9</v>
+        <v>2.14</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24880,10 +24880,10 @@
         <v>0</v>
       </c>
       <c r="AE124" t="n">
-        <v>1.93</v>
+        <v>1.66</v>
       </c>
       <c r="AF124" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AG124" t="n">
         <v>0</v>
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,22 +25575,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25668,10 +25668,10 @@
         <v>0</v>
       </c>
       <c r="AE128" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF128" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG128" t="n">
         <v>0</v>
@@ -25772,22 +25772,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q129" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25865,10 +25865,10 @@
         <v>0</v>
       </c>
       <c r="AE129" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF129" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG129" t="n">
         <v>0</v>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.48</v>
+        <v>3.71</v>
       </c>
       <c r="R133" t="n">
-        <v>2.06</v>
+        <v>3.61</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="Q134" t="n">
-        <v>3.71</v>
+        <v>3.48</v>
       </c>
       <c r="R134" t="n">
-        <v>3.61</v>
+        <v>2.06</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="Q135" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="R135" t="n">
-        <v>4.61</v>
+        <v>5.08</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27047,10 +27047,10 @@
         <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF135" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG135" t="n">
         <v>0</v>
@@ -27348,22 +27348,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,22 +27545,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1.68</v>
+        <v>2.6</v>
       </c>
       <c r="Q139" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="R139" t="n">
-        <v>5.08</v>
+        <v>2.62</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27835,10 +27835,10 @@
         <v>0</v>
       </c>
       <c r="AE139" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF139" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG139" t="n">
         <v>0</v>
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>2.6</v>
+        <v>1.77</v>
       </c>
       <c r="Q140" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="R140" t="n">
-        <v>2.62</v>
+        <v>4.61</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28032,10 +28032,10 @@
         <v>0</v>
       </c>
       <c r="AE140" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="AF140" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AG140" t="n">
         <v>0</v>
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29707,12 +29707,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q149" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R149" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29895,7 +29895,7 @@
         <v>0</v>
       </c>
       <c r="BI149" s="3" t="n">
-        <v>46118.625</v>
+        <v>46118.63541666666</v>
       </c>
     </row>
     <row r="150">
@@ -29904,12 +29904,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>2.13</v>
+        <v>1.84</v>
       </c>
       <c r="Q150" t="n">
-        <v>3.42</v>
+        <v>3.72</v>
       </c>
       <c r="R150" t="n">
-        <v>3.21</v>
+        <v>4.35</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30092,7 +30092,7 @@
         <v>0</v>
       </c>
       <c r="BI150" s="3" t="n">
-        <v>46118.63541666666</v>
+        <v>46118.64583333334</v>
       </c>
     </row>
     <row r="151">
@@ -30101,12 +30101,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="Q151" t="n">
-        <v>3.72</v>
+        <v>3.64</v>
       </c>
       <c r="R151" t="n">
-        <v>4.35</v>
+        <v>3.63</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30199,10 +30199,10 @@
         <v>0</v>
       </c>
       <c r="AE151" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF151" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG151" t="n">
         <v>0</v>
@@ -30289,7 +30289,7 @@
         <v>0</v>
       </c>
       <c r="BI151" s="3" t="n">
-        <v>46118.64583333334</v>
+        <v>46118.65625</v>
       </c>
     </row>
     <row r="152">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>1.94</v>
+        <v>2.62</v>
       </c>
       <c r="Q152" t="n">
-        <v>3.64</v>
+        <v>3.13</v>
       </c>
       <c r="R152" t="n">
-        <v>3.63</v>
+        <v>3.19</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30396,10 +30396,10 @@
         <v>0</v>
       </c>
       <c r="AE152" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AF152" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AG152" t="n">
         <v>0</v>
@@ -30495,12 +30495,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Q153" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R153" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30593,10 +30593,10 @@
         <v>0</v>
       </c>
       <c r="AE153" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF153" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG153" t="n">
         <v>0</v>
@@ -30683,7 +30683,7 @@
         <v>0</v>
       </c>
       <c r="BI153" s="3" t="n">
-        <v>46118.65625</v>
+        <v>46118.66666666666</v>
       </c>
     </row>
     <row r="154">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q155" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R155" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -31086,12 +31086,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>3.55</v>
+        <v>12.49</v>
       </c>
       <c r="Q156" t="n">
-        <v>3.7</v>
+        <v>6.92</v>
       </c>
       <c r="R156" t="n">
-        <v>1.92</v>
+        <v>1.2</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31184,10 +31184,10 @@
         <v>0</v>
       </c>
       <c r="AE156" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF156" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG156" t="n">
         <v>0</v>
@@ -31274,7 +31274,7 @@
         <v>0</v>
       </c>
       <c r="BI156" s="3" t="n">
-        <v>46118.66666666666</v>
+        <v>46118.69791666666</v>
       </c>
     </row>
     <row r="157">
@@ -31283,27 +31283,27 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>12.49</v>
+        <v>0</v>
       </c>
       <c r="Q157" t="n">
-        